--- a/YES BANK - AI Audit Intelligence - Effort Estimate.xlsx
+++ b/YES BANK - AI Audit Intelligence - Effort Estimate.xlsx
@@ -1043,7 +1043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="0010385A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1202,43 +1202,43 @@
       </c>
       <c r="D7" s="10">
         <f>'1. CCM'!V31</f>
-        <v/>
+        <v>2499</v>
       </c>
       <c r="E7" s="10">
         <f>D7/8</f>
-        <v/>
+        <v>312.375</v>
       </c>
       <c r="F7" s="11">
         <f>'1. CCM'!$AB$5</f>
-        <v/>
+        <v>16708220</v>
       </c>
       <c r="G7" s="12">
         <f>'1. CCM'!G39</f>
-        <v/>
+        <v>6000000</v>
       </c>
       <c r="H7" s="13">
         <f>IFERROR(G7/F7,0)</f>
-        <v/>
+        <v>0.3591046802112972</v>
       </c>
       <c r="I7" s="11">
         <f>'1. CCM'!$AB$6</f>
-        <v/>
+        <v>4297200</v>
       </c>
       <c r="J7" s="11">
         <f>G7*5%</f>
-        <v/>
+        <v>300000</v>
       </c>
       <c r="K7" s="11">
         <f>I7+J7</f>
-        <v/>
+        <v>4597200</v>
       </c>
       <c r="L7" s="11">
         <f>G7-K7</f>
-        <v/>
+        <v>1402800</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7/G7,0)</f>
-        <v/>
+        <v>0.2338</v>
       </c>
     </row>
     <row r="8">
@@ -1255,43 +1255,43 @@
       </c>
       <c r="D8" s="10">
         <f>'2. Pre-Audit Checks'!V30</f>
-        <v/>
+        <v>2185</v>
       </c>
       <c r="E8" s="10">
         <f>D8/8</f>
-        <v/>
+        <v>273.125</v>
       </c>
       <c r="F8" s="11">
         <f>'2. Pre-Audit Checks'!$AB$5</f>
-        <v/>
+        <v>14252160</v>
       </c>
       <c r="G8" s="12">
         <f>'2. Pre-Audit Checks'!G38</f>
-        <v/>
+        <v>5000000</v>
       </c>
       <c r="H8" s="13">
         <f>IFERROR(G8/F8,0)</f>
-        <v/>
+        <v>0.35082401544748304</v>
       </c>
       <c r="I8" s="11">
         <f>'2. Pre-Audit Checks'!$AB$6</f>
-        <v/>
+        <v>3627768</v>
       </c>
       <c r="J8" s="11">
         <f>G8*5%</f>
-        <v/>
+        <v>250000</v>
       </c>
       <c r="K8" s="11">
         <f>I8+J8</f>
-        <v/>
+        <v>3877768</v>
       </c>
       <c r="L8" s="11">
         <f>G8-K8</f>
-        <v/>
+        <v>1122232</v>
       </c>
       <c r="M8" s="14">
         <f>IFERROR(L8/G8,0)</f>
-        <v/>
+        <v>0.2244464</v>
       </c>
     </row>
     <row r="9">
@@ -1308,43 +1308,43 @@
       </c>
       <c r="D9" s="10">
         <f>'3. VKYC Audit'!V28</f>
-        <v/>
+        <v>1625</v>
       </c>
       <c r="E9" s="10">
         <f>D9/8</f>
-        <v/>
+        <v>203.125</v>
       </c>
       <c r="F9" s="11">
         <f>'3. VKYC Audit'!$AB$5</f>
-        <v/>
+        <v>10865330</v>
       </c>
       <c r="G9" s="12">
         <f>'3. VKYC Audit'!G36</f>
-        <v/>
+        <v>4250000</v>
       </c>
       <c r="H9" s="13">
         <f>IFERROR(G9/F9,0)</f>
-        <v/>
+        <v>0.39115240862449646</v>
       </c>
       <c r="I9" s="11">
         <f>'3. VKYC Audit'!$AB$6</f>
-        <v/>
+        <v>2780592</v>
       </c>
       <c r="J9" s="11">
         <f>G9*5%</f>
-        <v/>
+        <v>212500</v>
       </c>
       <c r="K9" s="11">
         <f>I9+J9</f>
-        <v/>
+        <v>2993092</v>
       </c>
       <c r="L9" s="11">
         <f>G9-K9</f>
-        <v/>
+        <v>1256908</v>
       </c>
       <c r="M9" s="14">
         <f>IFERROR(L9/G9,0)</f>
-        <v/>
+        <v>0.2957430588235294</v>
       </c>
     </row>
     <row r="10">
@@ -1361,43 +1361,43 @@
       </c>
       <c r="D10" s="10">
         <f>'4. KYC Audit'!V33</f>
-        <v/>
+        <v>2333</v>
       </c>
       <c r="E10" s="10">
         <f>D10/8</f>
-        <v/>
+        <v>291.625</v>
       </c>
       <c r="F10" s="11">
         <f>'4. KYC Audit'!$AB$5</f>
-        <v/>
+        <v>14999420</v>
       </c>
       <c r="G10" s="12">
         <f>'4. KYC Audit'!G41</f>
-        <v/>
+        <v>5500000</v>
       </c>
       <c r="H10" s="13">
         <f>IFERROR(G10/F10,0)</f>
-        <v/>
+        <v>0.36668084499267306</v>
       </c>
       <c r="I10" s="11">
         <f>'4. KYC Audit'!$AB$6</f>
-        <v/>
+        <v>3796320</v>
       </c>
       <c r="J10" s="11">
         <f>G10*5%</f>
-        <v/>
+        <v>275000</v>
       </c>
       <c r="K10" s="11">
         <f>I10+J10</f>
-        <v/>
+        <v>4071320</v>
       </c>
       <c r="L10" s="11">
         <f>G10-K10</f>
-        <v/>
+        <v>1428680</v>
       </c>
       <c r="M10" s="14">
         <f>IFERROR(L10/G10,0)</f>
-        <v/>
+        <v>0.25976</v>
       </c>
     </row>
     <row r="11">
@@ -1414,43 +1414,43 @@
       </c>
       <c r="D11" s="10">
         <f>'5. Checklist Automation'!V28</f>
-        <v/>
+        <v>1287</v>
       </c>
       <c r="E11" s="10">
         <f>D11/8</f>
-        <v/>
+        <v>160.875</v>
       </c>
       <c r="F11" s="11">
         <f>'5. Checklist Automation'!$AB$5</f>
-        <v/>
+        <v>8438810</v>
       </c>
       <c r="G11" s="12">
         <f>'5. Checklist Automation'!G36</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="H11" s="13">
         <f>IFERROR(G11/F11,0)</f>
-        <v/>
+        <v>0.38512539090227177</v>
       </c>
       <c r="I11" s="11">
         <f>'5. Checklist Automation'!$AB$6</f>
-        <v/>
+        <v>2152848</v>
       </c>
       <c r="J11" s="11">
         <f>G11*5%</f>
-        <v/>
+        <v>162500</v>
       </c>
       <c r="K11" s="11">
         <f>I11+J11</f>
-        <v/>
+        <v>2315348</v>
       </c>
       <c r="L11" s="11">
         <f>G11-K11</f>
-        <v/>
+        <v>934652</v>
       </c>
       <c r="M11" s="14">
         <f>IFERROR(L11/G11,0)</f>
-        <v/>
+        <v>0.28758523076923076</v>
       </c>
     </row>
     <row r="12">
@@ -1467,43 +1467,43 @@
       </c>
       <c r="D12" s="10">
         <f>'6. Data Analytics'!V34</f>
-        <v/>
+        <v>2542</v>
       </c>
       <c r="E12" s="10">
         <f>D12/8</f>
-        <v/>
+        <v>317.75</v>
       </c>
       <c r="F12" s="11">
         <f>'6. Data Analytics'!$AB$5</f>
-        <v/>
+        <v>16830130</v>
       </c>
       <c r="G12" s="12">
         <f>'6. Data Analytics'!G42</f>
-        <v/>
+        <v>6750000</v>
       </c>
       <c r="H12" s="13">
         <f>IFERROR(G12/F12,0)</f>
-        <v/>
+        <v>0.4010664207584849</v>
       </c>
       <c r="I12" s="11">
         <f>'6. Data Analytics'!$AB$6</f>
-        <v/>
+        <v>4322544</v>
       </c>
       <c r="J12" s="11">
         <f>G12*5%</f>
-        <v/>
+        <v>337500</v>
       </c>
       <c r="K12" s="11">
         <f>I12+J12</f>
-        <v/>
+        <v>4660044</v>
       </c>
       <c r="L12" s="11">
         <f>G12-K12</f>
-        <v/>
+        <v>2089956</v>
       </c>
       <c r="M12" s="14">
         <f>IFERROR(L12/G12,0)</f>
-        <v/>
+        <v>0.3096231111111111</v>
       </c>
     </row>
     <row r="13">
@@ -1520,43 +1520,43 @@
       </c>
       <c r="D13" s="10">
         <f>'7. ALCM'!V31</f>
-        <v/>
+        <v>2133</v>
       </c>
       <c r="E13" s="10">
         <f>D13/8</f>
-        <v/>
+        <v>266.625</v>
       </c>
       <c r="F13" s="11">
         <f>'7. ALCM'!$AB$5</f>
-        <v/>
+        <v>13756660</v>
       </c>
       <c r="G13" s="12">
         <f>'7. ALCM'!G39</f>
-        <v/>
+        <v>4750000</v>
       </c>
       <c r="H13" s="13">
         <f>IFERROR(G13/F13,0)</f>
-        <v/>
+        <v>0.3452873008419195</v>
       </c>
       <c r="I13" s="11">
         <f>'7. ALCM'!$AB$6</f>
-        <v/>
+        <v>3493176</v>
       </c>
       <c r="J13" s="11">
         <f>G13*5%</f>
-        <v/>
+        <v>237500</v>
       </c>
       <c r="K13" s="11">
         <f>I13+J13</f>
-        <v/>
+        <v>3730676</v>
       </c>
       <c r="L13" s="11">
         <f>G13-K13</f>
-        <v/>
+        <v>1019324</v>
       </c>
       <c r="M13" s="14">
         <f>IFERROR(L13/G13,0)</f>
-        <v/>
+        <v>0.21459452631578949</v>
       </c>
     </row>
     <row r="14">
@@ -1573,43 +1573,43 @@
       </c>
       <c r="D14" s="10">
         <f>'8. Agentic AI'!V36</f>
-        <v/>
+        <v>3168</v>
       </c>
       <c r="E14" s="10">
         <f>D14/8</f>
-        <v/>
+        <v>396</v>
       </c>
       <c r="F14" s="11">
         <f>'8. Agentic AI'!$AB$5</f>
-        <v/>
+        <v>21105589.999999996</v>
       </c>
       <c r="G14" s="12">
         <f>'8. Agentic AI'!G44</f>
-        <v/>
+        <v>8750000</v>
       </c>
       <c r="H14" s="13">
         <f>IFERROR(G14/F14,0)</f>
-        <v/>
+        <v>0.4145821083419133</v>
       </c>
       <c r="I14" s="11">
         <f>'8. Agentic AI'!$AB$6</f>
-        <v/>
+        <v>5428344</v>
       </c>
       <c r="J14" s="11">
         <f>G14*5%</f>
-        <v/>
+        <v>437500</v>
       </c>
       <c r="K14" s="11">
         <f>I14+J14</f>
-        <v/>
+        <v>5865844</v>
       </c>
       <c r="L14" s="11">
         <f>G14-K14</f>
-        <v/>
+        <v>2884156</v>
       </c>
       <c r="M14" s="14">
         <f>IFERROR(L14/G14,0)</f>
-        <v/>
+        <v>0.3296178285714286</v>
       </c>
     </row>
     <row r="15">
@@ -1626,43 +1626,43 @@
       </c>
       <c r="D15" s="10">
         <f>'9. ChatBot'!V28</f>
-        <v/>
+        <v>1319</v>
       </c>
       <c r="E15" s="10">
         <f>D15/8</f>
-        <v/>
+        <v>164.875</v>
       </c>
       <c r="F15" s="11">
         <f>'9. ChatBot'!$AB$5</f>
-        <v/>
+        <v>8575590</v>
       </c>
       <c r="G15" s="12">
         <f>'9. ChatBot'!G36</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="H15" s="13">
         <f>IFERROR(G15/F15,0)</f>
-        <v/>
+        <v>0.37898267058010005</v>
       </c>
       <c r="I15" s="11">
         <f>'9. ChatBot'!$AB$6</f>
-        <v/>
+        <v>2198736</v>
       </c>
       <c r="J15" s="11">
         <f>G15*5%</f>
-        <v/>
+        <v>162500</v>
       </c>
       <c r="K15" s="11">
         <f>I15+J15</f>
-        <v/>
+        <v>2361236</v>
       </c>
       <c r="L15" s="11">
         <f>G15-K15</f>
-        <v/>
+        <v>888764</v>
       </c>
       <c r="M15" s="14">
         <f>IFERROR(L15/G15,0)</f>
-        <v/>
+        <v>0.27346584615384617</v>
       </c>
     </row>
     <row r="16">
@@ -1674,47 +1674,47 @@
       </c>
       <c r="C16" s="17">
         <f>SUM(C7:C15)</f>
-        <v/>
+        <v>207</v>
       </c>
       <c r="D16" s="18">
         <f>SUM(D7:D15)</f>
-        <v/>
+        <v>19091</v>
       </c>
       <c r="E16" s="18">
         <f>SUM(E7:E15)</f>
-        <v/>
+        <v>2386.375</v>
       </c>
       <c r="F16" s="19">
         <f>SUM(F7:F15)</f>
-        <v/>
+        <v>125531910</v>
       </c>
       <c r="G16" s="19">
         <f>SUM(G7:G15)</f>
-        <v/>
+        <v>47500000</v>
       </c>
       <c r="H16" s="20">
         <f>IFERROR(G16/F16,0)</f>
-        <v/>
+        <v>0.37838984525926517</v>
       </c>
       <c r="I16" s="19">
         <f>SUM(I7:I15)</f>
-        <v/>
+        <v>32097528</v>
       </c>
       <c r="J16" s="19">
         <f>SUM(J7:J15)</f>
-        <v/>
+        <v>2375000</v>
       </c>
       <c r="K16" s="19">
         <f>SUM(K7:K15)</f>
-        <v/>
+        <v>34472528</v>
       </c>
       <c r="L16" s="19">
         <f>SUM(L7:L15)</f>
-        <v/>
+        <v>13027472</v>
       </c>
       <c r="M16" s="20">
         <f>IFERROR(L16/G16,0)</f>
-        <v/>
+        <v>0.2742625684210526</v>
       </c>
     </row>
     <row r="18">
@@ -1750,25 +1750,25 @@
     <row r="19">
       <c r="A19" s="23">
         <f>D16</f>
-        <v/>
+        <v>19091</v>
       </c>
       <c r="B19" s="24" t="n"/>
       <c r="C19" s="24" t="n"/>
       <c r="D19" s="23">
         <f>E16</f>
-        <v/>
+        <v>2386.375</v>
       </c>
       <c r="E19" s="24" t="n"/>
       <c r="F19" s="24" t="n"/>
       <c r="G19" s="25">
         <f>F16</f>
-        <v/>
+        <v>125531910</v>
       </c>
       <c r="H19" s="24" t="n"/>
       <c r="I19" s="24" t="n"/>
       <c r="J19" s="25">
         <f>G16</f>
-        <v/>
+        <v>47500000</v>
       </c>
       <c r="K19" s="24" t="n"/>
       <c r="L19" s="24" t="n"/>
@@ -1806,25 +1806,25 @@
     <row r="22">
       <c r="A22" s="26">
         <f>H16</f>
-        <v/>
+        <v>0.37838984525926517</v>
       </c>
       <c r="B22" s="24" t="n"/>
       <c r="C22" s="24" t="n"/>
       <c r="D22" s="26">
         <f>M16</f>
-        <v/>
+        <v>0.2742625684210526</v>
       </c>
       <c r="E22" s="24" t="n"/>
       <c r="F22" s="24" t="n"/>
       <c r="G22" s="23">
         <f>IFERROR(G16/D16,0)</f>
-        <v/>
+        <v>2488.083390079095</v>
       </c>
       <c r="H22" s="24" t="n"/>
       <c r="I22" s="24" t="n"/>
       <c r="J22" s="23">
         <f>IFERROR(I16/D16,0)</f>
-        <v/>
+        <v>1681.2910795662879</v>
       </c>
       <c r="K22" s="24" t="n"/>
       <c r="L22" s="24" t="n"/>
@@ -1876,15 +1876,15 @@
       </c>
       <c r="C27" s="31">
         <f>'1. CCM'!J31+'2. Pre-Audit Checks'!J30+'3. VKYC Audit'!J28+'4. KYC Audit'!J33+'5. Checklist Automation'!J28+'6. Data Analytics'!J34+'7. ALCM'!J31+'8. Agentic AI'!J36+'9. ChatBot'!J28</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="D27" s="13">
         <f>IFERROR(C27/$C$39,0)</f>
-        <v/>
+        <v>0.0022523702268084436</v>
       </c>
       <c r="E27" s="32">
         <f>C27*Ratesheet!$F$7</f>
-        <v/>
+        <v>928799.9999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1900,15 +1900,15 @@
       </c>
       <c r="C28" s="31">
         <f>'1. CCM'!K31+'2. Pre-Audit Checks'!K30+'3. VKYC Audit'!K28+'4. KYC Audit'!K33+'5. Checklist Automation'!K28+'6. Data Analytics'!K34+'7. ALCM'!K31+'8. Agentic AI'!K36+'9. ChatBot'!K28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D28" s="13">
         <f>IFERROR(C28/$C$39,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E28" s="32">
         <f>C28*Ratesheet!$F$8</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1924,15 +1924,15 @@
       </c>
       <c r="C29" s="31">
         <f>'1. CCM'!L31+'2. Pre-Audit Checks'!L30+'3. VKYC Audit'!L28+'4. KYC Audit'!L33+'5. Checklist Automation'!L28+'6. Data Analytics'!L34+'7. ALCM'!L31+'8. Agentic AI'!L36+'9. ChatBot'!L28</f>
-        <v/>
+        <v>452</v>
       </c>
       <c r="D29" s="13">
         <f>IFERROR(C29/$C$39,0)</f>
-        <v/>
+        <v>0.023676077732963176</v>
       </c>
       <c r="E29" s="32">
         <f>C29*Ratesheet!$F$9</f>
-        <v/>
+        <v>4339200</v>
       </c>
     </row>
     <row r="30">
@@ -1948,15 +1948,15 @@
       </c>
       <c r="C30" s="31">
         <f>'1. CCM'!M31+'2. Pre-Audit Checks'!M30+'3. VKYC Audit'!M28+'4. KYC Audit'!M33+'5. Checklist Automation'!M28+'6. Data Analytics'!M34+'7. ALCM'!M31+'8. Agentic AI'!M36+'9. ChatBot'!M28</f>
-        <v/>
+        <v>1330</v>
       </c>
       <c r="D30" s="13">
         <f>IFERROR(C30/$C$39,0)</f>
-        <v/>
+        <v>0.06966633492221466</v>
       </c>
       <c r="E30" s="32">
         <f>C30*Ratesheet!$F$10</f>
-        <v/>
+        <v>7341600</v>
       </c>
     </row>
     <row r="31">
@@ -1972,15 +1972,15 @@
       </c>
       <c r="C31" s="31">
         <f>'1. CCM'!N31+'2. Pre-Audit Checks'!N30+'3. VKYC Audit'!N28+'4. KYC Audit'!N33+'5. Checklist Automation'!N28+'6. Data Analytics'!N34+'7. ALCM'!N31+'8. Agentic AI'!N36+'9. ChatBot'!N28</f>
-        <v/>
+        <v>890</v>
       </c>
       <c r="D31" s="13">
         <f>IFERROR(C31/$C$39,0)</f>
-        <v/>
+        <v>0.046618825624639884</v>
       </c>
       <c r="E31" s="32">
         <f>C31*Ratesheet!$F$11</f>
-        <v/>
+        <v>3310800</v>
       </c>
     </row>
     <row r="32">
@@ -1996,15 +1996,15 @@
       </c>
       <c r="C32" s="31">
         <f>'1. CCM'!O31+'2. Pre-Audit Checks'!O30+'3. VKYC Audit'!O28+'4. KYC Audit'!O33+'5. Checklist Automation'!O28+'6. Data Analytics'!O34+'7. ALCM'!O31+'8. Agentic AI'!O36+'9. ChatBot'!O28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D32" s="13">
         <f>IFERROR(C32/$C$39,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E32" s="32">
         <f>C32*Ratesheet!$F$12</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2020,15 +2020,15 @@
       </c>
       <c r="C33" s="31">
         <f>'1. CCM'!P31+'2. Pre-Audit Checks'!P30+'3. VKYC Audit'!P28+'4. KYC Audit'!P33+'5. Checklist Automation'!P28+'6. Data Analytics'!P34+'7. ALCM'!P31+'8. Agentic AI'!P36+'9. ChatBot'!P28</f>
-        <v/>
+        <v>2836</v>
       </c>
       <c r="D33" s="13">
         <f>IFERROR(C33/$C$39,0)</f>
-        <v/>
+        <v>0.14855167356345922</v>
       </c>
       <c r="E33" s="32">
         <f>C33*Ratesheet!$F$13</f>
-        <v/>
+        <v>4594320</v>
       </c>
     </row>
     <row r="34">
@@ -2044,15 +2044,15 @@
       </c>
       <c r="C34" s="31">
         <f>'1. CCM'!Q31+'2. Pre-Audit Checks'!Q30+'3. VKYC Audit'!Q28+'4. KYC Audit'!Q33+'5. Checklist Automation'!Q28+'6. Data Analytics'!Q34+'7. ALCM'!Q31+'8. Agentic AI'!Q36+'9. ChatBot'!Q28</f>
-        <v/>
+        <v>3636</v>
       </c>
       <c r="D34" s="13">
         <f>IFERROR(C34/$C$39,0)</f>
-        <v/>
+        <v>0.1904562359226861</v>
       </c>
       <c r="E34" s="32">
         <f>C34*Ratesheet!$F$14</f>
-        <v/>
+        <v>4035960</v>
       </c>
     </row>
     <row r="35">
@@ -2068,15 +2068,15 @@
       </c>
       <c r="C35" s="31">
         <f>'1. CCM'!R31+'2. Pre-Audit Checks'!R30+'3. VKYC Audit'!R28+'4. KYC Audit'!R33+'5. Checklist Automation'!R28+'6. Data Analytics'!R34+'7. ALCM'!R31+'8. Agentic AI'!R36+'9. ChatBot'!R28</f>
-        <v/>
+        <v>4952</v>
       </c>
       <c r="D35" s="13">
         <f>IFERROR(C35/$C$39,0)</f>
-        <v/>
+        <v>0.25938924100361427</v>
       </c>
       <c r="E35" s="32">
         <f>C35*Ratesheet!$F$15</f>
-        <v/>
+        <v>4278528</v>
       </c>
     </row>
     <row r="36">
@@ -2092,15 +2092,15 @@
       </c>
       <c r="C36" s="31">
         <f>'1. CCM'!S31+'2. Pre-Audit Checks'!S30+'3. VKYC Audit'!S28+'4. KYC Audit'!S33+'5. Checklist Automation'!S28+'6. Data Analytics'!S34+'7. ALCM'!S31+'8. Agentic AI'!S36+'9. ChatBot'!S28</f>
-        <v/>
+        <v>4952</v>
       </c>
       <c r="D36" s="13">
         <f>IFERROR(C36/$C$39,0)</f>
-        <v/>
+        <v>0.25938924100361427</v>
       </c>
       <c r="E36" s="32">
         <f>C36*Ratesheet!$F$16</f>
-        <v/>
+        <v>3268320</v>
       </c>
     </row>
     <row r="37">
@@ -2116,15 +2116,15 @@
       </c>
       <c r="C37" s="31">
         <f>'1. CCM'!T31+'2. Pre-Audit Checks'!T30+'3. VKYC Audit'!T28+'4. KYC Audit'!T33+'5. Checklist Automation'!T28+'6. Data Analytics'!T34+'7. ALCM'!T31+'8. Agentic AI'!T36+'9. ChatBot'!T28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D37" s="13">
         <f>IFERROR(C37/$C$39,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E37" s="32">
         <f>C37*Ratesheet!$F$17</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2140,15 +2140,15 @@
       </c>
       <c r="C38" s="31">
         <f>'1. CCM'!U31+'2. Pre-Audit Checks'!U30+'3. VKYC Audit'!U28+'4. KYC Audit'!U33+'5. Checklist Automation'!U28+'6. Data Analytics'!U34+'7. ALCM'!U31+'8. Agentic AI'!U36+'9. ChatBot'!U28</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D38" s="13">
         <f>IFERROR(C38/$C$39,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E38" s="32">
         <f>C38*Ratesheet!$F$18</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2160,15 +2160,15 @@
       <c r="B39" s="34" t="n"/>
       <c r="C39" s="35">
         <f>SUM(C27:C38)</f>
-        <v/>
+        <v>19091</v>
       </c>
       <c r="D39" s="36">
         <f>SUM(D27:D38)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E39" s="37">
         <f>SUM(E27:E38)</f>
-        <v/>
+        <v>32097528</v>
       </c>
     </row>
     <row r="47">
@@ -2311,24 +2311,24 @@
     <mergeCell ref="A57:M57"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId10"/>
+    <hyperlink ref="M2" ns1:id="rId1"/>
+    <hyperlink ref="B7" ns1:id="rId2"/>
+    <hyperlink ref="B8" ns1:id="rId3"/>
+    <hyperlink ref="B9" ns1:id="rId4"/>
+    <hyperlink ref="B10" ns1:id="rId5"/>
+    <hyperlink ref="B11" ns1:id="rId6"/>
+    <hyperlink ref="B12" ns1:id="rId7"/>
+    <hyperlink ref="B13" ns1:id="rId8"/>
+    <hyperlink ref="B14" ns1:id="rId9"/>
+    <hyperlink ref="B15" ns1:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+  <drawing ns1:id="rId11"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00E57200"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2438,7 +2438,7 @@
       <c r="AA5" s="24" t="n"/>
       <c r="AB5" s="55">
         <f>SUMPRODUCT(J36:U36,Ratesheet!$B$23:$M$23)</f>
-        <v/>
+        <v>21105589.999999996</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -2544,7 +2544,7 @@
       <c r="AA6" s="24" t="n"/>
       <c r="AB6" s="55">
         <f>SUMPRODUCT(J36:U36,Ratesheet!$B$24:$M$24)</f>
-        <v/>
+        <v>5428344</v>
       </c>
     </row>
     <row r="7">
@@ -2593,7 +2593,7 @@
       <c r="AA7" s="24" t="n"/>
       <c r="AB7" s="10">
         <f>IFERROR(AB5/V36,0)</f>
-        <v/>
+        <v>6662.118055555555</v>
       </c>
     </row>
     <row r="8">
@@ -2653,7 +2653,7 @@
       <c r="U8" s="59" t="n"/>
       <c r="V8" s="60">
         <f>SUM(J8:U8)</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="Z8" s="30" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="10">
         <f>IFERROR(AB6/V36,0)</f>
-        <v/>
+        <v>1713.4924242424242</v>
       </c>
     </row>
     <row r="9">
@@ -2711,7 +2711,7 @@
       <c r="U9" s="59" t="n"/>
       <c r="V9" s="60">
         <f>SUM(J9:U9)</f>
-        <v/>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -2757,7 +2757,7 @@
       <c r="U10" s="59" t="n"/>
       <c r="V10" s="60">
         <f>SUM(J10:U10)</f>
-        <v/>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -2803,7 +2803,7 @@
       <c r="U11" s="59" t="n"/>
       <c r="V11" s="60">
         <f>SUM(J11:U11)</f>
-        <v/>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -2849,7 +2849,7 @@
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60">
         <f>SUM(J12:U12)</f>
-        <v/>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -2895,7 +2895,7 @@
       <c r="U13" s="59" t="n"/>
       <c r="V13" s="60">
         <f>SUM(J13:U13)</f>
-        <v/>
+        <v>144</v>
       </c>
     </row>
     <row r="14">
@@ -2941,7 +2941,7 @@
       <c r="U14" s="59" t="n"/>
       <c r="V14" s="60">
         <f>SUM(J14:U14)</f>
-        <v/>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -2987,7 +2987,7 @@
       <c r="U15" s="59" t="n"/>
       <c r="V15" s="60">
         <f>SUM(J15:U15)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
     <row r="16">
@@ -3033,7 +3033,7 @@
       <c r="U16" s="59" t="n"/>
       <c r="V16" s="60">
         <f>SUM(J16:U16)</f>
-        <v/>
+        <v>148</v>
       </c>
     </row>
     <row r="17">
@@ -3079,7 +3079,7 @@
       <c r="U17" s="59" t="n"/>
       <c r="V17" s="60">
         <f>SUM(J17:U17)</f>
-        <v/>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -3123,7 +3123,7 @@
       <c r="U18" s="59" t="n"/>
       <c r="V18" s="60">
         <f>SUM(J18:U18)</f>
-        <v/>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
@@ -3169,7 +3169,7 @@
       <c r="U19" s="59" t="n"/>
       <c r="V19" s="60">
         <f>SUM(J19:U19)</f>
-        <v/>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
@@ -3213,7 +3213,7 @@
       <c r="U20" s="59" t="n"/>
       <c r="V20" s="60">
         <f>SUM(J20:U20)</f>
-        <v/>
+        <v>98</v>
       </c>
     </row>
     <row r="21">
@@ -3259,7 +3259,7 @@
       <c r="U21" s="59" t="n"/>
       <c r="V21" s="60">
         <f>SUM(J21:U21)</f>
-        <v/>
+        <v>130</v>
       </c>
     </row>
     <row r="22">
@@ -3305,7 +3305,7 @@
       <c r="U22" s="59" t="n"/>
       <c r="V22" s="60">
         <f>SUM(J22:U22)</f>
-        <v/>
+        <v>122</v>
       </c>
     </row>
     <row r="23">
@@ -3351,7 +3351,7 @@
       <c r="U23" s="59" t="n"/>
       <c r="V23" s="60">
         <f>SUM(J23:U23)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
@@ -3397,7 +3397,7 @@
       <c r="U24" s="59" t="n"/>
       <c r="V24" s="60">
         <f>SUM(J24:U24)</f>
-        <v/>
+        <v>124</v>
       </c>
     </row>
     <row r="25">
@@ -3443,7 +3443,7 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="60">
         <f>SUM(J25:U25)</f>
-        <v/>
+        <v>94</v>
       </c>
     </row>
     <row r="26">
@@ -3487,7 +3487,7 @@
       <c r="U26" s="59" t="n"/>
       <c r="V26" s="60">
         <f>SUM(J26:U26)</f>
-        <v/>
+        <v>106</v>
       </c>
     </row>
     <row r="27">
@@ -3531,7 +3531,7 @@
       <c r="U27" s="59" t="n"/>
       <c r="V27" s="60">
         <f>SUM(J27:U27)</f>
-        <v/>
+        <v>136</v>
       </c>
     </row>
     <row r="28">
@@ -3575,7 +3575,7 @@
       <c r="U28" s="59" t="n"/>
       <c r="V28" s="60">
         <f>SUM(J28:U28)</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
@@ -3619,7 +3619,7 @@
       <c r="U29" s="59" t="n"/>
       <c r="V29" s="60">
         <f>SUM(J29:U29)</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="30">
@@ -3665,7 +3665,7 @@
       <c r="U30" s="59" t="n"/>
       <c r="V30" s="60">
         <f>SUM(J30:U30)</f>
-        <v/>
+        <v>134</v>
       </c>
     </row>
     <row r="31">
@@ -3711,7 +3711,7 @@
       <c r="U31" s="59" t="n"/>
       <c r="V31" s="60">
         <f>SUM(J31:U31)</f>
-        <v/>
+        <v>95</v>
       </c>
     </row>
     <row r="32">
@@ -3755,7 +3755,7 @@
       <c r="U32" s="59" t="n"/>
       <c r="V32" s="60">
         <f>SUM(J32:U32)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
@@ -3791,7 +3791,7 @@
       <c r="U33" s="59" t="n"/>
       <c r="V33" s="60">
         <f>SUM(J33:U33)</f>
-        <v/>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
@@ -3835,7 +3835,7 @@
       <c r="U34" s="59" t="n"/>
       <c r="V34" s="60">
         <f>SUM(J34:U34)</f>
-        <v/>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
@@ -3883,7 +3883,7 @@
       <c r="U35" s="59" t="n"/>
       <c r="V35" s="60">
         <f>SUM(J35:U35)</f>
-        <v/>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -3897,55 +3897,55 @@
       <c r="I36" s="34" t="n"/>
       <c r="J36" s="61">
         <f>SUM(J8:J35)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K36" s="61">
         <f>SUM(K8:K35)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L36" s="61">
         <f>SUM(L8:L35)</f>
-        <v/>
+        <v>85</v>
       </c>
       <c r="M36" s="61">
         <f>SUM(M8:M35)</f>
-        <v/>
+        <v>238</v>
       </c>
       <c r="N36" s="61">
         <f>SUM(N8:N35)</f>
-        <v/>
+        <v>140</v>
       </c>
       <c r="O36" s="61">
         <f>SUM(O8:O35)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P36" s="61">
         <f>SUM(P8:P35)</f>
-        <v/>
+        <v>472</v>
       </c>
       <c r="Q36" s="61">
         <f>SUM(Q8:Q35)</f>
-        <v/>
+        <v>596</v>
       </c>
       <c r="R36" s="61">
         <f>SUM(R8:R35)</f>
-        <v/>
+        <v>816</v>
       </c>
       <c r="S36" s="61">
         <f>SUM(S8:S35)</f>
-        <v/>
+        <v>816</v>
       </c>
       <c r="T36" s="61">
         <f>SUM(T8:T35)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U36" s="61">
         <f>SUM(U8:U35)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V36" s="62">
         <f>SUM(V8:V35)</f>
-        <v/>
+        <v>3168</v>
       </c>
     </row>
     <row r="38">
@@ -3956,51 +3956,51 @@
       </c>
       <c r="J38" s="64">
         <f>IFERROR(J36/$V$36,0)</f>
-        <v/>
+        <v>0.0015782828282828283</v>
       </c>
       <c r="K38" s="64">
         <f>IFERROR(K36/$V$36,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L38" s="64">
         <f>IFERROR(L36/$V$36,0)</f>
-        <v/>
+        <v>0.02683080808080808</v>
       </c>
       <c r="M38" s="64">
         <f>IFERROR(M36/$V$36,0)</f>
-        <v/>
+        <v>0.07512626262626262</v>
       </c>
       <c r="N38" s="64">
         <f>IFERROR(N36/$V$36,0)</f>
-        <v/>
+        <v>0.04419191919191919</v>
       </c>
       <c r="O38" s="64">
         <f>IFERROR(O36/$V$36,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P38" s="64">
         <f>IFERROR(P36/$V$36,0)</f>
-        <v/>
+        <v>0.14898989898989898</v>
       </c>
       <c r="Q38" s="64">
         <f>IFERROR(Q36/$V$36,0)</f>
-        <v/>
+        <v>0.18813131313131312</v>
       </c>
       <c r="R38" s="64">
         <f>IFERROR(R36/$V$36,0)</f>
-        <v/>
+        <v>0.25757575757575757</v>
       </c>
       <c r="S38" s="64">
         <f>IFERROR(S36/$V$36,0)</f>
-        <v/>
+        <v>0.25757575757575757</v>
       </c>
       <c r="T38" s="64">
         <f>IFERROR(T36/$V$36,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U38" s="64">
         <f>IFERROR(U36/$V$36,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4015,9 +4015,9 @@
       <c r="E41" s="65" t="n"/>
       <c r="F41" s="65" t="n"/>
       <c r="G41" s="65" t="n"/>
-      <c r="H41" s="66">
+      <c r="H41" s="66" t="str">
         <f>" All Values in ( "&amp;C7&amp;" )"</f>
-        <v/>
+        <v> All Values in ( INR )</v>
       </c>
       <c r="I41" s="24" t="n"/>
       <c r="L41" s="67" t="inlineStr">
@@ -4113,12 +4113,12 @@
       <c r="P43" s="24" t="n"/>
       <c r="Q43" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>21105589.999999996</v>
       </c>
       <c r="R43" s="24" t="n"/>
       <c r="S43" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>21105589.999999996</v>
       </c>
     </row>
     <row r="44">
@@ -4129,24 +4129,24 @@
       </c>
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="24" t="n"/>
-      <c r="D44" s="8">
+      <c r="D44" s="8" t="str">
         <f>C4</f>
-        <v/>
+        <v>India - R&amp;C</v>
       </c>
       <c r="F44" s="31">
         <f>V36</f>
-        <v/>
+        <v>3168</v>
       </c>
       <c r="G44" s="32">
         <f>D42-(SUM(G45:G48)+H49)</f>
-        <v/>
+        <v>8750000</v>
       </c>
       <c r="H44" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="30">
+      <c r="L44" s="30" t="str">
         <f>"Proposed Fee (Home Office)"&amp;" - "&amp;IF(D44=0,"",D44)</f>
-        <v/>
+        <v>Proposed Fee (Home Office) - India - R&amp;C</v>
       </c>
       <c r="M44" s="24" t="n"/>
       <c r="N44" s="24" t="n"/>
@@ -4154,12 +4154,12 @@
       <c r="P44" s="24" t="n"/>
       <c r="Q44" s="12">
         <f>G44</f>
-        <v/>
+        <v>8750000</v>
       </c>
       <c r="R44" s="73" t="n"/>
       <c r="S44" s="11">
         <f>S43*S47</f>
-        <v/>
+        <v>8750000</v>
       </c>
     </row>
     <row r="45">
@@ -4192,12 +4192,12 @@
       <c r="P45" s="24" t="n"/>
       <c r="Q45" s="11">
         <f>Q43-Q44</f>
-        <v/>
+        <v>12355589.999999996</v>
       </c>
       <c r="R45" s="24" t="n"/>
       <c r="S45" s="11">
         <f>S43-S44</f>
-        <v/>
+        <v>12355589.999999996</v>
       </c>
     </row>
     <row r="46">
@@ -4225,12 +4225,12 @@
       <c r="P46" s="24" t="n"/>
       <c r="Q46" s="74">
         <f>IFERROR(Q45/Q43,0)</f>
-        <v/>
+        <v>0.5854178916580867</v>
       </c>
       <c r="R46" s="24" t="n"/>
       <c r="S46" s="74">
         <f>1-S47</f>
-        <v/>
+        <v>0.5854178916580868</v>
       </c>
     </row>
     <row r="47">
@@ -4258,12 +4258,12 @@
       <c r="P47" s="24" t="n"/>
       <c r="Q47" s="75">
         <f>1-Q46</f>
-        <v/>
+        <v>0.4145821083419133</v>
       </c>
       <c r="R47" s="24" t="n"/>
       <c r="S47" s="76">
         <f>F51</f>
-        <v/>
+        <v>0.4145821083419133</v>
       </c>
     </row>
     <row r="48">
@@ -4298,15 +4298,15 @@
       <c r="E49" s="34" t="n"/>
       <c r="F49" s="78">
         <f>SUM(F44:F48)</f>
-        <v/>
+        <v>3168</v>
       </c>
       <c r="G49" s="79">
         <f>SUM(G44:G48)</f>
-        <v/>
+        <v>8750000</v>
       </c>
       <c r="H49" s="79">
         <f>SUM(H44:H48)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F51" s="81">
         <f>IFERROR(G44/$AB$5,0)</f>
-        <v/>
+        <v>0.4145821083419133</v>
       </c>
       <c r="G51" s="24" t="n"/>
     </row>
@@ -4392,43 +4392,43 @@
       </c>
     </row>
     <row r="54">
-      <c r="K54" s="67">
+      <c r="K54" s="67" t="str">
         <f>C7</f>
-        <v/>
+        <v>INR</v>
       </c>
       <c r="L54" s="11">
         <f>G49</f>
-        <v/>
+        <v>8750000</v>
       </c>
       <c r="M54" s="10">
         <f>IFERROR(L54/F49,0)</f>
-        <v/>
+        <v>2761.9949494949497</v>
       </c>
       <c r="N54" s="11">
         <f>G44</f>
-        <v/>
+        <v>8750000</v>
       </c>
       <c r="O54" s="10">
         <f>IFERROR(N54/V36,0)</f>
-        <v/>
+        <v>2761.9949494949497</v>
       </c>
       <c r="P54" s="83">
         <f>IFERROR((T54-(N54*5%))/N54,0)</f>
-        <v/>
+        <v>0.3296178285714286</v>
       </c>
       <c r="Q54" s="84" t="n"/>
       <c r="R54" s="83">
         <f>IFERROR((L54-V54-(G49-G44)-(N54*5%))/L54,0)</f>
-        <v/>
+        <v>0.3296178285714286</v>
       </c>
       <c r="S54" s="84" t="n"/>
       <c r="T54" s="11">
         <f>IFERROR(N54-V54,0)</f>
-        <v/>
+        <v>3321656</v>
       </c>
       <c r="V54" s="11">
         <f>IFERROR($AB$6,0)</f>
-        <v/>
+        <v>5428344</v>
       </c>
     </row>
     <row r="56">
@@ -4548,15 +4548,15 @@
     <mergeCell ref="Q47:R47"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId2"/>
+    <hyperlink ref="X4" ns1:id="rId1"/>
+    <hyperlink ref="X6" ns1:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00E57200"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4666,7 +4666,7 @@
       <c r="AA5" s="24" t="n"/>
       <c r="AB5" s="55">
         <f>SUMPRODUCT(J28:U28,Ratesheet!$B$23:$M$23)</f>
-        <v/>
+        <v>8575590</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -4772,7 +4772,7 @@
       <c r="AA6" s="24" t="n"/>
       <c r="AB6" s="55">
         <f>SUMPRODUCT(J28:U28,Ratesheet!$B$24:$M$24)</f>
-        <v/>
+        <v>2198736</v>
       </c>
     </row>
     <row r="7">
@@ -4821,7 +4821,7 @@
       <c r="AA7" s="24" t="n"/>
       <c r="AB7" s="10">
         <f>IFERROR(AB5/V28,0)</f>
-        <v/>
+        <v>6501.58453373768</v>
       </c>
     </row>
     <row r="8">
@@ -4881,7 +4881,7 @@
       <c r="U8" s="59" t="n"/>
       <c r="V8" s="60">
         <f>SUM(J8:U8)</f>
-        <v/>
+        <v>69</v>
       </c>
       <c r="Z8" s="30" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
       <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="10">
         <f>IFERROR(AB6/V28,0)</f>
-        <v/>
+        <v>1666.9719484457923</v>
       </c>
     </row>
     <row r="9">
@@ -4939,7 +4939,7 @@
       <c r="U9" s="59" t="n"/>
       <c r="V9" s="60">
         <f>SUM(J9:U9)</f>
-        <v/>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -4985,7 +4985,7 @@
       <c r="U10" s="59" t="n"/>
       <c r="V10" s="60">
         <f>SUM(J10:U10)</f>
-        <v/>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -5031,7 +5031,7 @@
       <c r="U11" s="59" t="n"/>
       <c r="V11" s="60">
         <f>SUM(J11:U11)</f>
-        <v/>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -5077,7 +5077,7 @@
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60">
         <f>SUM(J12:U12)</f>
-        <v/>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -5123,7 +5123,7 @@
       <c r="U13" s="59" t="n"/>
       <c r="V13" s="60">
         <f>SUM(J13:U13)</f>
-        <v/>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
@@ -5169,7 +5169,7 @@
       <c r="U14" s="59" t="n"/>
       <c r="V14" s="60">
         <f>SUM(J14:U14)</f>
-        <v/>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -5213,7 +5213,7 @@
       <c r="U15" s="59" t="n"/>
       <c r="V15" s="60">
         <f>SUM(J15:U15)</f>
-        <v/>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -5257,7 +5257,7 @@
       <c r="U16" s="59" t="n"/>
       <c r="V16" s="60">
         <f>SUM(J16:U16)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
@@ -5301,7 +5301,7 @@
       <c r="U17" s="59" t="n"/>
       <c r="V17" s="60">
         <f>SUM(J17:U17)</f>
-        <v/>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -5345,7 +5345,7 @@
       <c r="U18" s="59" t="n"/>
       <c r="V18" s="60">
         <f>SUM(J18:U18)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5391,7 +5391,7 @@
       <c r="U19" s="59" t="n"/>
       <c r="V19" s="60">
         <f>SUM(J19:U19)</f>
-        <v/>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -5435,7 +5435,7 @@
       <c r="U20" s="59" t="n"/>
       <c r="V20" s="60">
         <f>SUM(J20:U20)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
@@ -5481,7 +5481,7 @@
       <c r="U21" s="59" t="n"/>
       <c r="V21" s="60">
         <f>SUM(J21:U21)</f>
-        <v/>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
@@ -5527,7 +5527,7 @@
       <c r="U22" s="59" t="n"/>
       <c r="V22" s="60">
         <f>SUM(J22:U22)</f>
-        <v/>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
@@ -5573,7 +5573,7 @@
       <c r="U23" s="59" t="n"/>
       <c r="V23" s="60">
         <f>SUM(J23:U23)</f>
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
@@ -5617,7 +5617,7 @@
       <c r="U24" s="59" t="n"/>
       <c r="V24" s="60">
         <f>SUM(J24:U24)</f>
-        <v/>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -5653,7 +5653,7 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="60">
         <f>SUM(J25:U25)</f>
-        <v/>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -5697,7 +5697,7 @@
       <c r="U26" s="59" t="n"/>
       <c r="V26" s="60">
         <f>SUM(J26:U26)</f>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -5745,7 +5745,7 @@
       <c r="U27" s="59" t="n"/>
       <c r="V27" s="60">
         <f>SUM(J27:U27)</f>
-        <v/>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
@@ -5759,55 +5759,55 @@
       <c r="I28" s="34" t="n"/>
       <c r="J28" s="61">
         <f>SUM(J8:J27)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="K28" s="61">
         <f>SUM(K8:K27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L28" s="61">
         <f>SUM(L8:L27)</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="M28" s="61">
         <f>SUM(M8:M27)</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="N28" s="61">
         <f>SUM(N8:N27)</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="O28" s="61">
         <f>SUM(O8:O27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P28" s="61">
         <f>SUM(P8:P27)</f>
-        <v/>
+        <v>188</v>
       </c>
       <c r="Q28" s="61">
         <f>SUM(Q8:Q27)</f>
-        <v/>
+        <v>264</v>
       </c>
       <c r="R28" s="61">
         <f>SUM(R8:R27)</f>
-        <v/>
+        <v>344</v>
       </c>
       <c r="S28" s="61">
         <f>SUM(S8:S27)</f>
-        <v/>
+        <v>344</v>
       </c>
       <c r="T28" s="61">
         <f>SUM(T8:T27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U28" s="61">
         <f>SUM(U8:U27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V28" s="62">
         <f>SUM(V8:V27)</f>
-        <v/>
+        <v>1319</v>
       </c>
     </row>
     <row r="30">
@@ -5818,51 +5818,51 @@
       </c>
       <c r="J30" s="64">
         <f>IFERROR(J28/$V$28,0)</f>
-        <v/>
+        <v>0.002274450341167551</v>
       </c>
       <c r="K30" s="64">
         <f>IFERROR(K28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L30" s="64">
         <f>IFERROR(L28/$V$28,0)</f>
-        <v/>
+        <v>0.024260803639120546</v>
       </c>
       <c r="M30" s="64">
         <f>IFERROR(M28/$V$28,0)</f>
-        <v/>
+        <v>0.0712661106899166</v>
       </c>
       <c r="N30" s="64">
         <f>IFERROR(N28/$V$28,0)</f>
-        <v/>
+        <v>0.03790750568612585</v>
       </c>
       <c r="O30" s="64">
         <f>IFERROR(O28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P30" s="64">
         <f>IFERROR(P28/$V$28,0)</f>
-        <v/>
+        <v>0.1425322213798332</v>
       </c>
       <c r="Q30" s="64">
         <f>IFERROR(Q28/$V$28,0)</f>
-        <v/>
+        <v>0.2001516300227445</v>
       </c>
       <c r="R30" s="64">
         <f>IFERROR(R28/$V$28,0)</f>
-        <v/>
+        <v>0.2608036391205459</v>
       </c>
       <c r="S30" s="64">
         <f>IFERROR(S28/$V$28,0)</f>
-        <v/>
+        <v>0.2608036391205459</v>
       </c>
       <c r="T30" s="64">
         <f>IFERROR(T28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U30" s="64">
         <f>IFERROR(U28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -5877,9 +5877,9 @@
       <c r="E33" s="65" t="n"/>
       <c r="F33" s="65" t="n"/>
       <c r="G33" s="65" t="n"/>
-      <c r="H33" s="66">
+      <c r="H33" s="66" t="str">
         <f>" All Values in ( "&amp;C7&amp;" )"</f>
-        <v/>
+        <v> All Values in ( INR )</v>
       </c>
       <c r="I33" s="24" t="n"/>
       <c r="L33" s="67" t="inlineStr">
@@ -5975,12 +5975,12 @@
       <c r="P35" s="24" t="n"/>
       <c r="Q35" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>8575590</v>
       </c>
       <c r="R35" s="24" t="n"/>
       <c r="S35" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>8575590</v>
       </c>
     </row>
     <row r="36">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="24" t="n"/>
-      <c r="D36" s="8">
+      <c r="D36" s="8" t="str">
         <f>C4</f>
-        <v/>
+        <v>India - R&amp;C</v>
       </c>
       <c r="F36" s="31">
         <f>V28</f>
-        <v/>
+        <v>1319</v>
       </c>
       <c r="G36" s="32">
         <f>D34-(SUM(G37:G40)+H41)</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="H36" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="30">
+      <c r="L36" s="30" t="str">
         <f>"Proposed Fee (Home Office)"&amp;" - "&amp;IF(D36=0,"",D36)</f>
-        <v/>
+        <v>Proposed Fee (Home Office) - India - R&amp;C</v>
       </c>
       <c r="M36" s="24" t="n"/>
       <c r="N36" s="24" t="n"/>
@@ -6016,12 +6016,12 @@
       <c r="P36" s="24" t="n"/>
       <c r="Q36" s="12">
         <f>G36</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="R36" s="73" t="n"/>
       <c r="S36" s="11">
         <f>S35*S39</f>
-        <v/>
+        <v>3250000</v>
       </c>
     </row>
     <row r="37">
@@ -6054,12 +6054,12 @@
       <c r="P37" s="24" t="n"/>
       <c r="Q37" s="11">
         <f>Q35-Q36</f>
-        <v/>
+        <v>5325590</v>
       </c>
       <c r="R37" s="24" t="n"/>
       <c r="S37" s="11">
         <f>S35-S36</f>
-        <v/>
+        <v>5325590</v>
       </c>
     </row>
     <row r="38">
@@ -6087,12 +6087,12 @@
       <c r="P38" s="24" t="n"/>
       <c r="Q38" s="74">
         <f>IFERROR(Q37/Q35,0)</f>
-        <v/>
+        <v>0.6210173294199</v>
       </c>
       <c r="R38" s="24" t="n"/>
       <c r="S38" s="74">
         <f>1-S39</f>
-        <v/>
+        <v>0.6210173294199</v>
       </c>
     </row>
     <row r="39">
@@ -6120,12 +6120,12 @@
       <c r="P39" s="24" t="n"/>
       <c r="Q39" s="75">
         <f>1-Q38</f>
-        <v/>
+        <v>0.37898267058010005</v>
       </c>
       <c r="R39" s="24" t="n"/>
       <c r="S39" s="76">
         <f>F43</f>
-        <v/>
+        <v>0.37898267058010005</v>
       </c>
     </row>
     <row r="40">
@@ -6160,15 +6160,15 @@
       <c r="E41" s="34" t="n"/>
       <c r="F41" s="78">
         <f>SUM(F36:F40)</f>
-        <v/>
+        <v>1319</v>
       </c>
       <c r="G41" s="79">
         <f>SUM(G36:G40)</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="H41" s="79">
         <f>SUM(H36:H40)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="F43" s="81">
         <f>IFERROR(G36/$AB$5,0)</f>
-        <v/>
+        <v>0.37898267058010005</v>
       </c>
       <c r="G43" s="24" t="n"/>
     </row>
@@ -6254,43 +6254,43 @@
       </c>
     </row>
     <row r="46">
-      <c r="K46" s="67">
+      <c r="K46" s="67" t="str">
         <f>C7</f>
-        <v/>
+        <v>INR</v>
       </c>
       <c r="L46" s="11">
         <f>G41</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="M46" s="10">
         <f>IFERROR(L46/F41,0)</f>
-        <v/>
+        <v>2463.9878695981806</v>
       </c>
       <c r="N46" s="11">
         <f>G36</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="O46" s="10">
         <f>IFERROR(N46/V28,0)</f>
-        <v/>
+        <v>2463.9878695981806</v>
       </c>
       <c r="P46" s="83">
         <f>IFERROR((T46-(N46*5%))/N46,0)</f>
-        <v/>
+        <v>0.27346584615384617</v>
       </c>
       <c r="Q46" s="84" t="n"/>
       <c r="R46" s="83">
         <f>IFERROR((L46-V46-(G41-G36)-(N46*5%))/L46,0)</f>
-        <v/>
+        <v>0.27346584615384617</v>
       </c>
       <c r="S46" s="84" t="n"/>
       <c r="T46" s="11">
         <f>IFERROR(N46-V46,0)</f>
-        <v/>
+        <v>1051264</v>
       </c>
       <c r="V46" s="11">
         <f>IFERROR($AB$6,0)</f>
-        <v/>
+        <v>2198736</v>
       </c>
     </row>
     <row r="48">
@@ -6402,15 +6402,15 @@
     <mergeCell ref="A33:G33"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId2"/>
+    <hyperlink ref="X4" ns1:id="rId1"/>
+    <hyperlink ref="X6" ns1:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="0064748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6514,11 +6514,11 @@
       </c>
       <c r="E7" s="44">
         <f>C7*$C$4</f>
-        <v/>
+        <v>30030</v>
       </c>
       <c r="F7" s="44">
         <f>D7*$C$4</f>
-        <v/>
+        <v>21599.999999999996</v>
       </c>
     </row>
     <row r="8">
@@ -6540,11 +6540,11 @@
       </c>
       <c r="E8" s="44">
         <f>C8*$C$4</f>
-        <v/>
+        <v>25000</v>
       </c>
       <c r="F8" s="44">
         <f>D8*$C$4</f>
-        <v/>
+        <v>10000</v>
       </c>
     </row>
     <row r="9">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="E9" s="44">
         <f>C9*$C$4</f>
-        <v/>
+        <v>22080</v>
       </c>
       <c r="F9" s="44">
         <f>D9*$C$4</f>
-        <v/>
+        <v>9600</v>
       </c>
     </row>
     <row r="10">
@@ -6592,11 +6592,11 @@
       </c>
       <c r="E10" s="44">
         <f>C10*$C$4</f>
-        <v/>
+        <v>17540</v>
       </c>
       <c r="F10" s="44">
         <f>D10*$C$4</f>
-        <v/>
+        <v>5520</v>
       </c>
     </row>
     <row r="11">
@@ -6618,11 +6618,11 @@
       </c>
       <c r="E11" s="44">
         <f>C11*$C$4</f>
-        <v/>
+        <v>14909.999999999998</v>
       </c>
       <c r="F11" s="44">
         <f>D11*$C$4</f>
-        <v/>
+        <v>3720</v>
       </c>
     </row>
     <row r="12">
@@ -6644,11 +6644,11 @@
       </c>
       <c r="E12" s="44">
         <f>C12*$C$4</f>
-        <v/>
+        <v>10080</v>
       </c>
       <c r="F12" s="44">
         <f>D12*$C$4</f>
-        <v/>
+        <v>2520</v>
       </c>
     </row>
     <row r="13">
@@ -6670,11 +6670,11 @@
       </c>
       <c r="E13" s="44">
         <f>C13*$C$4</f>
-        <v/>
+        <v>7530</v>
       </c>
       <c r="F13" s="44">
         <f>D13*$C$4</f>
-        <v/>
+        <v>1620.0000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -6696,11 +6696,11 @@
       </c>
       <c r="E14" s="44">
         <f>C14*$C$4</f>
-        <v/>
+        <v>5040</v>
       </c>
       <c r="F14" s="44">
         <f>D14*$C$4</f>
-        <v/>
+        <v>1110</v>
       </c>
     </row>
     <row r="15">
@@ -6722,11 +6722,11 @@
       </c>
       <c r="E15" s="44">
         <f>C15*$C$4</f>
-        <v/>
+        <v>3980</v>
       </c>
       <c r="F15" s="44">
         <f>D15*$C$4</f>
-        <v/>
+        <v>864.0000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="E16" s="44">
         <f>C16*$C$4</f>
-        <v/>
+        <v>3690</v>
       </c>
       <c r="F16" s="44">
         <f>D16*$C$4</f>
-        <v/>
+        <v>660</v>
       </c>
     </row>
     <row r="17">
@@ -6774,11 +6774,11 @@
       </c>
       <c r="E17" s="44">
         <f>C17*$C$4</f>
-        <v/>
+        <v>3199.9999999999995</v>
       </c>
       <c r="F17" s="44">
         <f>D17*$C$4</f>
-        <v/>
+        <v>504</v>
       </c>
     </row>
     <row r="18">
@@ -6800,11 +6800,11 @@
       </c>
       <c r="E18" s="44">
         <f>C18*$C$4</f>
-        <v/>
+        <v>1630</v>
       </c>
       <c r="F18" s="44">
         <f>D18*$C$4</f>
-        <v/>
+        <v>300</v>
       </c>
     </row>
     <row r="21">
@@ -6889,51 +6889,51 @@
       </c>
       <c r="B23" s="49">
         <f>$E$7</f>
-        <v/>
+        <v>30030</v>
       </c>
       <c r="C23" s="49">
         <f>$E$8</f>
-        <v/>
+        <v>25000</v>
       </c>
       <c r="D23" s="49">
         <f>$E$9</f>
-        <v/>
+        <v>22080</v>
       </c>
       <c r="E23" s="49">
         <f>$E$10</f>
-        <v/>
+        <v>17540</v>
       </c>
       <c r="F23" s="49">
         <f>$E$11</f>
-        <v/>
+        <v>14909.999999999998</v>
       </c>
       <c r="G23" s="49">
         <f>$E$12</f>
-        <v/>
+        <v>10080</v>
       </c>
       <c r="H23" s="49">
         <f>$E$13</f>
-        <v/>
+        <v>7530</v>
       </c>
       <c r="I23" s="49">
         <f>$E$14</f>
-        <v/>
+        <v>5040</v>
       </c>
       <c r="J23" s="49">
         <f>$E$15</f>
-        <v/>
+        <v>3980</v>
       </c>
       <c r="K23" s="49">
         <f>$E$16</f>
-        <v/>
+        <v>3690</v>
       </c>
       <c r="L23" s="49">
         <f>$E$17</f>
-        <v/>
+        <v>3199.9999999999995</v>
       </c>
       <c r="M23" s="49">
         <f>$E$18</f>
-        <v/>
+        <v>1630</v>
       </c>
     </row>
     <row r="24">
@@ -6944,63 +6944,63 @@
       </c>
       <c r="B24" s="49">
         <f>$F$7</f>
-        <v/>
+        <v>21599.999999999996</v>
       </c>
       <c r="C24" s="49">
         <f>$F$8</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="D24" s="49">
         <f>$F$9</f>
-        <v/>
+        <v>9600</v>
       </c>
       <c r="E24" s="49">
         <f>$F$10</f>
-        <v/>
+        <v>5520</v>
       </c>
       <c r="F24" s="49">
         <f>$F$11</f>
-        <v/>
+        <v>3720</v>
       </c>
       <c r="G24" s="49">
         <f>$F$12</f>
-        <v/>
+        <v>2520</v>
       </c>
       <c r="H24" s="49">
         <f>$F$13</f>
-        <v/>
+        <v>1620.0000000000002</v>
       </c>
       <c r="I24" s="49">
         <f>$F$14</f>
-        <v/>
+        <v>1110</v>
       </c>
       <c r="J24" s="49">
         <f>$F$15</f>
-        <v/>
+        <v>864.0000000000001</v>
       </c>
       <c r="K24" s="49">
         <f>$F$16</f>
-        <v/>
+        <v>660</v>
       </c>
       <c r="L24" s="49">
         <f>$F$17</f>
-        <v/>
+        <v>504</v>
       </c>
       <c r="M24" s="49">
         <f>$F$18</f>
-        <v/>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId1"/>
+    <hyperlink ref="H4" ns1:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00E57200"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7110,7 +7110,7 @@
       <c r="AA5" s="24" t="n"/>
       <c r="AB5" s="55">
         <f>SUMPRODUCT(J31:U31,Ratesheet!$B$23:$M$23)</f>
-        <v/>
+        <v>16708220</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -7216,7 +7216,7 @@
       <c r="AA6" s="24" t="n"/>
       <c r="AB6" s="55">
         <f>SUMPRODUCT(J31:U31,Ratesheet!$B$24:$M$24)</f>
-        <v/>
+        <v>4297200</v>
       </c>
     </row>
     <row r="7">
@@ -7265,7 +7265,7 @@
       <c r="AA7" s="24" t="n"/>
       <c r="AB7" s="10">
         <f>IFERROR(AB5/V31,0)</f>
-        <v/>
+        <v>6685.962384953981</v>
       </c>
     </row>
     <row r="8">
@@ -7325,7 +7325,7 @@
       <c r="U8" s="59" t="n"/>
       <c r="V8" s="60">
         <f>SUM(J8:U8)</f>
-        <v/>
+        <v>114</v>
       </c>
       <c r="Z8" s="30" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
       <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="10">
         <f>IFERROR(AB6/V31,0)</f>
-        <v/>
+        <v>1719.5678271308523</v>
       </c>
     </row>
     <row r="9">
@@ -7383,7 +7383,7 @@
       <c r="U9" s="59" t="n"/>
       <c r="V9" s="60">
         <f>SUM(J9:U9)</f>
-        <v/>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -7431,7 +7431,7 @@
       <c r="U10" s="59" t="n"/>
       <c r="V10" s="60">
         <f>SUM(J10:U10)</f>
-        <v/>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -7477,7 +7477,7 @@
       <c r="U11" s="59" t="n"/>
       <c r="V11" s="60">
         <f>SUM(J11:U11)</f>
-        <v/>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -7523,7 +7523,7 @@
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60">
         <f>SUM(J12:U12)</f>
-        <v/>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -7569,7 +7569,7 @@
       <c r="U13" s="59" t="n"/>
       <c r="V13" s="60">
         <f>SUM(J13:U13)</f>
-        <v/>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -7615,7 +7615,7 @@
       <c r="U14" s="59" t="n"/>
       <c r="V14" s="60">
         <f>SUM(J14:U14)</f>
-        <v/>
+        <v>156</v>
       </c>
     </row>
     <row r="15">
@@ -7659,7 +7659,7 @@
       <c r="U15" s="59" t="n"/>
       <c r="V15" s="60">
         <f>SUM(J15:U15)</f>
-        <v/>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
@@ -7705,7 +7705,7 @@
       <c r="U16" s="59" t="n"/>
       <c r="V16" s="60">
         <f>SUM(J16:U16)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
@@ -7749,7 +7749,7 @@
       <c r="U17" s="59" t="n"/>
       <c r="V17" s="60">
         <f>SUM(J17:U17)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
@@ -7793,7 +7793,7 @@
       <c r="U18" s="59" t="n"/>
       <c r="V18" s="60">
         <f>SUM(J18:U18)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -7839,7 +7839,7 @@
       <c r="U19" s="59" t="n"/>
       <c r="V19" s="60">
         <f>SUM(J19:U19)</f>
-        <v/>
+        <v>136</v>
       </c>
     </row>
     <row r="20">
@@ -7883,7 +7883,7 @@
       <c r="U20" s="59" t="n"/>
       <c r="V20" s="60">
         <f>SUM(J20:U20)</f>
-        <v/>
+        <v>160</v>
       </c>
     </row>
     <row r="21">
@@ -7927,7 +7927,7 @@
       <c r="U21" s="59" t="n"/>
       <c r="V21" s="60">
         <f>SUM(J21:U21)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
@@ -7973,7 +7973,7 @@
       <c r="U22" s="59" t="n"/>
       <c r="V22" s="60">
         <f>SUM(J22:U22)</f>
-        <v/>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
@@ -8019,7 +8019,7 @@
       <c r="U23" s="59" t="n"/>
       <c r="V23" s="60">
         <f>SUM(J23:U23)</f>
-        <v/>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
@@ -8063,7 +8063,7 @@
       <c r="U24" s="59" t="n"/>
       <c r="V24" s="60">
         <f>SUM(J24:U24)</f>
-        <v/>
+        <v>92</v>
       </c>
     </row>
     <row r="25">
@@ -8109,7 +8109,7 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="60">
         <f>SUM(J25:U25)</f>
-        <v/>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
@@ -8155,7 +8155,7 @@
       <c r="U26" s="59" t="n"/>
       <c r="V26" s="60">
         <f>SUM(J26:U26)</f>
-        <v/>
+        <v>95</v>
       </c>
     </row>
     <row r="27">
@@ -8199,7 +8199,7 @@
       <c r="U27" s="59" t="n"/>
       <c r="V27" s="60">
         <f>SUM(J27:U27)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="28">
@@ -8235,7 +8235,7 @@
       <c r="U28" s="59" t="n"/>
       <c r="V28" s="60">
         <f>SUM(J28:U28)</f>
-        <v/>
+        <v>140</v>
       </c>
     </row>
     <row r="29">
@@ -8279,7 +8279,7 @@
       <c r="U29" s="59" t="n"/>
       <c r="V29" s="60">
         <f>SUM(J29:U29)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -8327,7 +8327,7 @@
       <c r="U30" s="59" t="n"/>
       <c r="V30" s="60">
         <f>SUM(J30:U30)</f>
-        <v/>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
@@ -8341,55 +8341,55 @@
       <c r="I31" s="34" t="n"/>
       <c r="J31" s="61">
         <f>SUM(J8:J30)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="K31" s="61">
         <f>SUM(K8:K30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L31" s="61">
         <f>SUM(L8:L30)</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="M31" s="61">
         <f>SUM(M8:M30)</f>
-        <v/>
+        <v>168</v>
       </c>
       <c r="N31" s="61">
         <f>SUM(N8:N30)</f>
-        <v/>
+        <v>140</v>
       </c>
       <c r="O31" s="61">
         <f>SUM(O8:O30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P31" s="61">
         <f>SUM(P8:P30)</f>
-        <v/>
+        <v>368</v>
       </c>
       <c r="Q31" s="61">
         <f>SUM(Q8:Q30)</f>
-        <v/>
+        <v>472</v>
       </c>
       <c r="R31" s="61">
         <f>SUM(R8:R30)</f>
-        <v/>
+        <v>640</v>
       </c>
       <c r="S31" s="61">
         <f>SUM(S8:S30)</f>
-        <v/>
+        <v>640</v>
       </c>
       <c r="T31" s="61">
         <f>SUM(T8:T30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U31" s="61">
         <f>SUM(U8:U30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V31" s="62">
         <f>SUM(V8:V30)</f>
-        <v/>
+        <v>2499</v>
       </c>
     </row>
     <row r="33">
@@ -8400,51 +8400,51 @@
       </c>
       <c r="J33" s="64">
         <f>IFERROR(J31/$V$31,0)</f>
-        <v/>
+        <v>0.0024009603841536613</v>
       </c>
       <c r="K33" s="64">
         <f>IFERROR(K31/$V$31,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L33" s="64">
         <f>IFERROR(L31/$V$31,0)</f>
-        <v/>
+        <v>0.026010404161664665</v>
       </c>
       <c r="M33" s="64">
         <f>IFERROR(M31/$V$31,0)</f>
-        <v/>
+        <v>0.06722689075630252</v>
       </c>
       <c r="N33" s="64">
         <f>IFERROR(N31/$V$31,0)</f>
-        <v/>
+        <v>0.056022408963585436</v>
       </c>
       <c r="O33" s="64">
         <f>IFERROR(O31/$V$31,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P33" s="64">
         <f>IFERROR(P31/$V$31,0)</f>
-        <v/>
+        <v>0.14725890356142457</v>
       </c>
       <c r="Q33" s="64">
         <f>IFERROR(Q31/$V$31,0)</f>
-        <v/>
+        <v>0.18887555022008803</v>
       </c>
       <c r="R33" s="64">
         <f>IFERROR(R31/$V$31,0)</f>
-        <v/>
+        <v>0.25610244097639057</v>
       </c>
       <c r="S33" s="64">
         <f>IFERROR(S31/$V$31,0)</f>
-        <v/>
+        <v>0.25610244097639057</v>
       </c>
       <c r="T33" s="64">
         <f>IFERROR(T31/$V$31,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U33" s="64">
         <f>IFERROR(U31/$V$31,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -8459,9 +8459,9 @@
       <c r="E36" s="65" t="n"/>
       <c r="F36" s="65" t="n"/>
       <c r="G36" s="65" t="n"/>
-      <c r="H36" s="66">
+      <c r="H36" s="66" t="str">
         <f>" All Values in ( "&amp;C7&amp;" )"</f>
-        <v/>
+        <v> All Values in ( INR )</v>
       </c>
       <c r="I36" s="24" t="n"/>
       <c r="L36" s="67" t="inlineStr">
@@ -8557,12 +8557,12 @@
       <c r="P38" s="24" t="n"/>
       <c r="Q38" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>16708220</v>
       </c>
       <c r="R38" s="24" t="n"/>
       <c r="S38" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>16708220</v>
       </c>
     </row>
     <row r="39">
@@ -8573,24 +8573,24 @@
       </c>
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="24" t="n"/>
-      <c r="D39" s="8">
+      <c r="D39" s="8" t="str">
         <f>C4</f>
-        <v/>
+        <v>India - R&amp;C</v>
       </c>
       <c r="F39" s="31">
         <f>V31</f>
-        <v/>
+        <v>2499</v>
       </c>
       <c r="G39" s="32">
         <f>D37-(SUM(G40:G43)+H44)</f>
-        <v/>
+        <v>6000000</v>
       </c>
       <c r="H39" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="30">
+      <c r="L39" s="30" t="str">
         <f>"Proposed Fee (Home Office)"&amp;" - "&amp;IF(D39=0,"",D39)</f>
-        <v/>
+        <v>Proposed Fee (Home Office) - India - R&amp;C</v>
       </c>
       <c r="M39" s="24" t="n"/>
       <c r="N39" s="24" t="n"/>
@@ -8598,12 +8598,12 @@
       <c r="P39" s="24" t="n"/>
       <c r="Q39" s="12">
         <f>G39</f>
-        <v/>
+        <v>6000000</v>
       </c>
       <c r="R39" s="73" t="n"/>
       <c r="S39" s="11">
         <f>S38*S42</f>
-        <v/>
+        <v>6000000</v>
       </c>
     </row>
     <row r="40">
@@ -8636,12 +8636,12 @@
       <c r="P40" s="24" t="n"/>
       <c r="Q40" s="11">
         <f>Q38-Q39</f>
-        <v/>
+        <v>10708220</v>
       </c>
       <c r="R40" s="24" t="n"/>
       <c r="S40" s="11">
         <f>S38-S39</f>
-        <v/>
+        <v>10708220</v>
       </c>
     </row>
     <row r="41">
@@ -8669,12 +8669,12 @@
       <c r="P41" s="24" t="n"/>
       <c r="Q41" s="74">
         <f>IFERROR(Q40/Q38,0)</f>
-        <v/>
+        <v>0.6408953197887028</v>
       </c>
       <c r="R41" s="24" t="n"/>
       <c r="S41" s="74">
         <f>1-S42</f>
-        <v/>
+        <v>0.6408953197887028</v>
       </c>
     </row>
     <row r="42">
@@ -8702,12 +8702,12 @@
       <c r="P42" s="24" t="n"/>
       <c r="Q42" s="75">
         <f>1-Q41</f>
-        <v/>
+        <v>0.3591046802112972</v>
       </c>
       <c r="R42" s="24" t="n"/>
       <c r="S42" s="76">
         <f>F46</f>
-        <v/>
+        <v>0.3591046802112972</v>
       </c>
     </row>
     <row r="43">
@@ -8742,15 +8742,15 @@
       <c r="E44" s="34" t="n"/>
       <c r="F44" s="78">
         <f>SUM(F39:F43)</f>
-        <v/>
+        <v>2499</v>
       </c>
       <c r="G44" s="79">
         <f>SUM(G39:G43)</f>
-        <v/>
+        <v>6000000</v>
       </c>
       <c r="H44" s="79">
         <f>SUM(H39:H43)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="F46" s="81">
         <f>IFERROR(G39/$AB$5,0)</f>
-        <v/>
+        <v>0.3591046802112972</v>
       </c>
       <c r="G46" s="24" t="n"/>
     </row>
@@ -8836,43 +8836,43 @@
       </c>
     </row>
     <row r="49">
-      <c r="K49" s="67">
+      <c r="K49" s="67" t="str">
         <f>C7</f>
-        <v/>
+        <v>INR</v>
       </c>
       <c r="L49" s="11">
         <f>G44</f>
-        <v/>
+        <v>6000000</v>
       </c>
       <c r="M49" s="10">
         <f>IFERROR(L49/F44,0)</f>
-        <v/>
+        <v>2400.9603841536614</v>
       </c>
       <c r="N49" s="11">
         <f>G39</f>
-        <v/>
+        <v>6000000</v>
       </c>
       <c r="O49" s="10">
         <f>IFERROR(N49/V31,0)</f>
-        <v/>
+        <v>2400.9603841536614</v>
       </c>
       <c r="P49" s="83">
         <f>IFERROR((T49-(N49*5%))/N49,0)</f>
-        <v/>
+        <v>0.2338</v>
       </c>
       <c r="Q49" s="84" t="n"/>
       <c r="R49" s="83">
         <f>IFERROR((L49-V49-(G44-G39)-(N49*5%))/L49,0)</f>
-        <v/>
+        <v>0.2338</v>
       </c>
       <c r="S49" s="84" t="n"/>
       <c r="T49" s="11">
         <f>IFERROR(N49-V49,0)</f>
-        <v/>
+        <v>1702800</v>
       </c>
       <c r="V49" s="11">
         <f>IFERROR($AB$6,0)</f>
-        <v/>
+        <v>4297200</v>
       </c>
     </row>
     <row r="51">
@@ -8987,15 +8987,15 @@
     <mergeCell ref="U6:U7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId2"/>
+    <hyperlink ref="X4" ns1:id="rId1"/>
+    <hyperlink ref="X6" ns1:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00E57200"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9105,7 +9105,7 @@
       <c r="AA5" s="24" t="n"/>
       <c r="AB5" s="55">
         <f>SUMPRODUCT(J30:U30,Ratesheet!$B$23:$M$23)</f>
-        <v/>
+        <v>14252160</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -9211,7 +9211,7 @@
       <c r="AA6" s="24" t="n"/>
       <c r="AB6" s="55">
         <f>SUMPRODUCT(J30:U30,Ratesheet!$B$24:$M$24)</f>
-        <v/>
+        <v>3627768</v>
       </c>
     </row>
     <row r="7">
@@ -9260,7 +9260,7 @@
       <c r="AA7" s="24" t="n"/>
       <c r="AB7" s="10">
         <f>IFERROR(AB5/V30,0)</f>
-        <v/>
+        <v>6522.727688787186</v>
       </c>
     </row>
     <row r="8">
@@ -9320,7 +9320,7 @@
       <c r="U8" s="59" t="n"/>
       <c r="V8" s="60">
         <f>SUM(J8:U8)</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="Z8" s="30" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
       <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="10">
         <f>IFERROR(AB6/V30,0)</f>
-        <v/>
+        <v>1660.3057208237985</v>
       </c>
     </row>
     <row r="9">
@@ -9378,7 +9378,7 @@
       <c r="U9" s="59" t="n"/>
       <c r="V9" s="60">
         <f>SUM(J9:U9)</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -9426,7 +9426,7 @@
       <c r="U10" s="59" t="n"/>
       <c r="V10" s="60">
         <f>SUM(J10:U10)</f>
-        <v/>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -9472,7 +9472,7 @@
       <c r="U11" s="59" t="n"/>
       <c r="V11" s="60">
         <f>SUM(J11:U11)</f>
-        <v/>
+        <v>192</v>
       </c>
     </row>
     <row r="12">
@@ -9516,7 +9516,7 @@
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60">
         <f>SUM(J12:U12)</f>
-        <v/>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -9562,7 +9562,7 @@
       <c r="U13" s="59" t="n"/>
       <c r="V13" s="60">
         <f>SUM(J13:U13)</f>
-        <v/>
+        <v>168</v>
       </c>
     </row>
     <row r="14">
@@ -9608,7 +9608,7 @@
       <c r="U14" s="59" t="n"/>
       <c r="V14" s="60">
         <f>SUM(J14:U14)</f>
-        <v/>
+        <v>126</v>
       </c>
     </row>
     <row r="15">
@@ -9654,7 +9654,7 @@
       <c r="U15" s="59" t="n"/>
       <c r="V15" s="60">
         <f>SUM(J15:U15)</f>
-        <v/>
+        <v>110</v>
       </c>
     </row>
     <row r="16">
@@ -9698,7 +9698,7 @@
       <c r="U16" s="59" t="n"/>
       <c r="V16" s="60">
         <f>SUM(J16:U16)</f>
-        <v/>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -9742,7 +9742,7 @@
       <c r="U17" s="59" t="n"/>
       <c r="V17" s="60">
         <f>SUM(J17:U17)</f>
-        <v/>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
@@ -9788,7 +9788,7 @@
       <c r="U18" s="59" t="n"/>
       <c r="V18" s="60">
         <f>SUM(J18:U18)</f>
-        <v/>
+        <v>108</v>
       </c>
     </row>
     <row r="19">
@@ -9832,7 +9832,7 @@
       <c r="U19" s="59" t="n"/>
       <c r="V19" s="60">
         <f>SUM(J19:U19)</f>
-        <v/>
+        <v>136</v>
       </c>
     </row>
     <row r="20">
@@ -9876,7 +9876,7 @@
       <c r="U20" s="59" t="n"/>
       <c r="V20" s="60">
         <f>SUM(J20:U20)</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="21">
@@ -9920,7 +9920,7 @@
       <c r="U21" s="59" t="n"/>
       <c r="V21" s="60">
         <f>SUM(J21:U21)</f>
-        <v/>
+        <v>98</v>
       </c>
     </row>
     <row r="22">
@@ -9964,7 +9964,7 @@
       <c r="U22" s="59" t="n"/>
       <c r="V22" s="60">
         <f>SUM(J22:U22)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -10008,7 +10008,7 @@
       <c r="U23" s="59" t="n"/>
       <c r="V23" s="60">
         <f>SUM(J23:U23)</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
@@ -10054,7 +10054,7 @@
       <c r="U24" s="59" t="n"/>
       <c r="V24" s="60">
         <f>SUM(J24:U24)</f>
-        <v/>
+        <v>112</v>
       </c>
     </row>
     <row r="25">
@@ -10100,7 +10100,7 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="60">
         <f>SUM(J25:U25)</f>
-        <v/>
+        <v>81</v>
       </c>
     </row>
     <row r="26">
@@ -10144,7 +10144,7 @@
       <c r="U26" s="59" t="n"/>
       <c r="V26" s="60">
         <f>SUM(J26:U26)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
@@ -10180,7 +10180,7 @@
       <c r="U27" s="59" t="n"/>
       <c r="V27" s="60">
         <f>SUM(J27:U27)</f>
-        <v/>
+        <v>110</v>
       </c>
     </row>
     <row r="28">
@@ -10224,7 +10224,7 @@
       <c r="U28" s="59" t="n"/>
       <c r="V28" s="60">
         <f>SUM(J28:U28)</f>
-        <v/>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
@@ -10272,7 +10272,7 @@
       <c r="U29" s="59" t="n"/>
       <c r="V29" s="60">
         <f>SUM(J29:U29)</f>
-        <v/>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
@@ -10286,55 +10286,55 @@
       <c r="I30" s="34" t="n"/>
       <c r="J30" s="61">
         <f>SUM(J8:J29)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="K30" s="61">
         <f>SUM(K8:K29)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L30" s="61">
         <f>SUM(L8:L29)</f>
-        <v/>
+        <v>47</v>
       </c>
       <c r="M30" s="61">
         <f>SUM(M8:M29)</f>
-        <v/>
+        <v>142</v>
       </c>
       <c r="N30" s="61">
         <f>SUM(N8:N29)</f>
-        <v/>
+        <v>110</v>
       </c>
       <c r="O30" s="61">
         <f>SUM(O8:O29)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P30" s="61">
         <f>SUM(P8:P29)</f>
-        <v/>
+        <v>324</v>
       </c>
       <c r="Q30" s="61">
         <f>SUM(Q8:Q29)</f>
-        <v/>
+        <v>412</v>
       </c>
       <c r="R30" s="61">
         <f>SUM(R8:R29)</f>
-        <v/>
+        <v>572</v>
       </c>
       <c r="S30" s="61">
         <f>SUM(S8:S29)</f>
-        <v/>
+        <v>572</v>
       </c>
       <c r="T30" s="61">
         <f>SUM(T8:T29)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U30" s="61">
         <f>SUM(U8:U29)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V30" s="62">
         <f>SUM(V8:V29)</f>
-        <v/>
+        <v>2185</v>
       </c>
     </row>
     <row r="32">
@@ -10345,51 +10345,51 @@
       </c>
       <c r="J32" s="64">
         <f>IFERROR(J30/$V$30,0)</f>
-        <v/>
+        <v>0.002745995423340961</v>
       </c>
       <c r="K32" s="64">
         <f>IFERROR(K30/$V$30,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L32" s="64">
         <f>IFERROR(L30/$V$30,0)</f>
-        <v/>
+        <v>0.021510297482837528</v>
       </c>
       <c r="M32" s="64">
         <f>IFERROR(M30/$V$30,0)</f>
-        <v/>
+        <v>0.06498855835240275</v>
       </c>
       <c r="N32" s="64">
         <f>IFERROR(N30/$V$30,0)</f>
-        <v/>
+        <v>0.05034324942791762</v>
       </c>
       <c r="O32" s="64">
         <f>IFERROR(O30/$V$30,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P32" s="64">
         <f>IFERROR(P30/$V$30,0)</f>
-        <v/>
+        <v>0.1482837528604119</v>
       </c>
       <c r="Q32" s="64">
         <f>IFERROR(Q30/$V$30,0)</f>
-        <v/>
+        <v>0.188558352402746</v>
       </c>
       <c r="R32" s="64">
         <f>IFERROR(R30/$V$30,0)</f>
-        <v/>
+        <v>0.2617848970251716</v>
       </c>
       <c r="S32" s="64">
         <f>IFERROR(S30/$V$30,0)</f>
-        <v/>
+        <v>0.2617848970251716</v>
       </c>
       <c r="T32" s="64">
         <f>IFERROR(T30/$V$30,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U32" s="64">
         <f>IFERROR(U30/$V$30,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -10404,9 +10404,9 @@
       <c r="E35" s="65" t="n"/>
       <c r="F35" s="65" t="n"/>
       <c r="G35" s="65" t="n"/>
-      <c r="H35" s="66">
+      <c r="H35" s="66" t="str">
         <f>" All Values in ( "&amp;C7&amp;" )"</f>
-        <v/>
+        <v> All Values in ( INR )</v>
       </c>
       <c r="I35" s="24" t="n"/>
       <c r="L35" s="67" t="inlineStr">
@@ -10502,12 +10502,12 @@
       <c r="P37" s="24" t="n"/>
       <c r="Q37" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>14252160</v>
       </c>
       <c r="R37" s="24" t="n"/>
       <c r="S37" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>14252160</v>
       </c>
     </row>
     <row r="38">
@@ -10518,24 +10518,24 @@
       </c>
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="24" t="n"/>
-      <c r="D38" s="8">
+      <c r="D38" s="8" t="str">
         <f>C4</f>
-        <v/>
+        <v>India - R&amp;C</v>
       </c>
       <c r="F38" s="31">
         <f>V30</f>
-        <v/>
+        <v>2185</v>
       </c>
       <c r="G38" s="32">
         <f>D36-(SUM(G39:G42)+H43)</f>
-        <v/>
+        <v>5000000</v>
       </c>
       <c r="H38" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="30">
+      <c r="L38" s="30" t="str">
         <f>"Proposed Fee (Home Office)"&amp;" - "&amp;IF(D38=0,"",D38)</f>
-        <v/>
+        <v>Proposed Fee (Home Office) - India - R&amp;C</v>
       </c>
       <c r="M38" s="24" t="n"/>
       <c r="N38" s="24" t="n"/>
@@ -10543,12 +10543,12 @@
       <c r="P38" s="24" t="n"/>
       <c r="Q38" s="12">
         <f>G38</f>
-        <v/>
+        <v>5000000</v>
       </c>
       <c r="R38" s="73" t="n"/>
       <c r="S38" s="11">
         <f>S37*S41</f>
-        <v/>
+        <v>5000000</v>
       </c>
     </row>
     <row r="39">
@@ -10581,12 +10581,12 @@
       <c r="P39" s="24" t="n"/>
       <c r="Q39" s="11">
         <f>Q37-Q38</f>
-        <v/>
+        <v>9252160</v>
       </c>
       <c r="R39" s="24" t="n"/>
       <c r="S39" s="11">
         <f>S37-S38</f>
-        <v/>
+        <v>9252160</v>
       </c>
     </row>
     <row r="40">
@@ -10614,12 +10614,12 @@
       <c r="P40" s="24" t="n"/>
       <c r="Q40" s="74">
         <f>IFERROR(Q39/Q37,0)</f>
-        <v/>
+        <v>0.6491759845525169</v>
       </c>
       <c r="R40" s="24" t="n"/>
       <c r="S40" s="74">
         <f>1-S41</f>
-        <v/>
+        <v>0.6491759845525169</v>
       </c>
     </row>
     <row r="41">
@@ -10647,12 +10647,12 @@
       <c r="P41" s="24" t="n"/>
       <c r="Q41" s="75">
         <f>1-Q40</f>
-        <v/>
+        <v>0.35082401544748304</v>
       </c>
       <c r="R41" s="24" t="n"/>
       <c r="S41" s="76">
         <f>F45</f>
-        <v/>
+        <v>0.35082401544748304</v>
       </c>
     </row>
     <row r="42">
@@ -10687,15 +10687,15 @@
       <c r="E43" s="34" t="n"/>
       <c r="F43" s="78">
         <f>SUM(F38:F42)</f>
-        <v/>
+        <v>2185</v>
       </c>
       <c r="G43" s="79">
         <f>SUM(G38:G42)</f>
-        <v/>
+        <v>5000000</v>
       </c>
       <c r="H43" s="79">
         <f>SUM(H38:H42)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="F45" s="81">
         <f>IFERROR(G38/$AB$5,0)</f>
-        <v/>
+        <v>0.35082401544748304</v>
       </c>
       <c r="G45" s="24" t="n"/>
     </row>
@@ -10781,43 +10781,43 @@
       </c>
     </row>
     <row r="48">
-      <c r="K48" s="67">
+      <c r="K48" s="67" t="str">
         <f>C7</f>
-        <v/>
+        <v>INR</v>
       </c>
       <c r="L48" s="11">
         <f>G43</f>
-        <v/>
+        <v>5000000</v>
       </c>
       <c r="M48" s="10">
         <f>IFERROR(L48/F43,0)</f>
-        <v/>
+        <v>2288.329519450801</v>
       </c>
       <c r="N48" s="11">
         <f>G38</f>
-        <v/>
+        <v>5000000</v>
       </c>
       <c r="O48" s="10">
         <f>IFERROR(N48/V30,0)</f>
-        <v/>
+        <v>2288.329519450801</v>
       </c>
       <c r="P48" s="83">
         <f>IFERROR((T48-(N48*5%))/N48,0)</f>
-        <v/>
+        <v>0.2244464</v>
       </c>
       <c r="Q48" s="84" t="n"/>
       <c r="R48" s="83">
         <f>IFERROR((L48-V48-(G43-G38)-(N48*5%))/L48,0)</f>
-        <v/>
+        <v>0.2244464</v>
       </c>
       <c r="S48" s="84" t="n"/>
       <c r="T48" s="11">
         <f>IFERROR(N48-V48,0)</f>
-        <v/>
+        <v>1372232</v>
       </c>
       <c r="V48" s="11">
         <f>IFERROR($AB$6,0)</f>
-        <v/>
+        <v>3627768</v>
       </c>
     </row>
     <row r="50">
@@ -10931,15 +10931,15 @@
     <mergeCell ref="E36:H36"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId2"/>
+    <hyperlink ref="X4" ns1:id="rId1"/>
+    <hyperlink ref="X6" ns1:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00E57200"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11049,7 +11049,7 @@
       <c r="AA5" s="24" t="n"/>
       <c r="AB5" s="55">
         <f>SUMPRODUCT(J28:U28,Ratesheet!$B$23:$M$23)</f>
-        <v/>
+        <v>10865330</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -11155,7 +11155,7 @@
       <c r="AA6" s="24" t="n"/>
       <c r="AB6" s="55">
         <f>SUMPRODUCT(J28:U28,Ratesheet!$B$24:$M$24)</f>
-        <v/>
+        <v>2780592</v>
       </c>
     </row>
     <row r="7">
@@ -11204,7 +11204,7 @@
       <c r="AA7" s="24" t="n"/>
       <c r="AB7" s="10">
         <f>IFERROR(AB5/V28,0)</f>
-        <v/>
+        <v>6686.3569230769235</v>
       </c>
     </row>
     <row r="8">
@@ -11264,7 +11264,7 @@
       <c r="U8" s="59" t="n"/>
       <c r="V8" s="60">
         <f>SUM(J8:U8)</f>
-        <v/>
+        <v>73</v>
       </c>
       <c r="Z8" s="30" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
       <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="10">
         <f>IFERROR(AB6/V28,0)</f>
-        <v/>
+        <v>1711.1335384615384</v>
       </c>
     </row>
     <row r="9">
@@ -11322,7 +11322,7 @@
       <c r="U9" s="59" t="n"/>
       <c r="V9" s="60">
         <f>SUM(J9:U9)</f>
-        <v/>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -11368,7 +11368,7 @@
       <c r="U10" s="59" t="n"/>
       <c r="V10" s="60">
         <f>SUM(J10:U10)</f>
-        <v/>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -11414,7 +11414,7 @@
       <c r="U11" s="59" t="n"/>
       <c r="V11" s="60">
         <f>SUM(J11:U11)</f>
-        <v/>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
@@ -11460,7 +11460,7 @@
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60">
         <f>SUM(J12:U12)</f>
-        <v/>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -11506,7 +11506,7 @@
       <c r="U13" s="59" t="n"/>
       <c r="V13" s="60">
         <f>SUM(J13:U13)</f>
-        <v/>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -11552,7 +11552,7 @@
       <c r="U14" s="59" t="n"/>
       <c r="V14" s="60">
         <f>SUM(J14:U14)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -11598,7 +11598,7 @@
       <c r="U15" s="59" t="n"/>
       <c r="V15" s="60">
         <f>SUM(J15:U15)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
     <row r="16">
@@ -11642,7 +11642,7 @@
       <c r="U16" s="59" t="n"/>
       <c r="V16" s="60">
         <f>SUM(J16:U16)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -11686,7 +11686,7 @@
       <c r="U17" s="59" t="n"/>
       <c r="V17" s="60">
         <f>SUM(J17:U17)</f>
-        <v/>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -11730,7 +11730,7 @@
       <c r="U18" s="59" t="n"/>
       <c r="V18" s="60">
         <f>SUM(J18:U18)</f>
-        <v/>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
@@ -11774,7 +11774,7 @@
       <c r="U19" s="59" t="n"/>
       <c r="V19" s="60">
         <f>SUM(J19:U19)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -11820,7 +11820,7 @@
       <c r="U20" s="59" t="n"/>
       <c r="V20" s="60">
         <f>SUM(J20:U20)</f>
-        <v/>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
@@ -11864,7 +11864,7 @@
       <c r="U21" s="59" t="n"/>
       <c r="V21" s="60">
         <f>SUM(J21:U21)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
@@ -11910,7 +11910,7 @@
       <c r="U22" s="59" t="n"/>
       <c r="V22" s="60">
         <f>SUM(J22:U22)</f>
-        <v/>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
@@ -11956,7 +11956,7 @@
       <c r="U23" s="59" t="n"/>
       <c r="V23" s="60">
         <f>SUM(J23:U23)</f>
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
@@ -12000,7 +12000,7 @@
       <c r="U24" s="59" t="n"/>
       <c r="V24" s="60">
         <f>SUM(J24:U24)</f>
-        <v/>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -12036,7 +12036,7 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="60">
         <f>SUM(J25:U25)</f>
-        <v/>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
@@ -12080,7 +12080,7 @@
       <c r="U26" s="59" t="n"/>
       <c r="V26" s="60">
         <f>SUM(J26:U26)</f>
-        <v/>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -12128,7 +12128,7 @@
       <c r="U27" s="59" t="n"/>
       <c r="V27" s="60">
         <f>SUM(J27:U27)</f>
-        <v/>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
@@ -12142,55 +12142,55 @@
       <c r="I28" s="34" t="n"/>
       <c r="J28" s="61">
         <f>SUM(J8:J27)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="K28" s="61">
         <f>SUM(K8:K27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L28" s="61">
         <f>SUM(L8:L27)</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="M28" s="61">
         <f>SUM(M8:M27)</f>
-        <v/>
+        <v>118</v>
       </c>
       <c r="N28" s="61">
         <f>SUM(N8:N27)</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="O28" s="61">
         <f>SUM(O8:O27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P28" s="61">
         <f>SUM(P8:P27)</f>
-        <v/>
+        <v>256</v>
       </c>
       <c r="Q28" s="61">
         <f>SUM(Q8:Q27)</f>
-        <v/>
+        <v>312</v>
       </c>
       <c r="R28" s="61">
         <f>SUM(R8:R27)</f>
-        <v/>
+        <v>408</v>
       </c>
       <c r="S28" s="61">
         <f>SUM(S8:S27)</f>
-        <v/>
+        <v>408</v>
       </c>
       <c r="T28" s="61">
         <f>SUM(T8:T27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U28" s="61">
         <f>SUM(U8:U27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V28" s="62">
         <f>SUM(V8:V27)</f>
-        <v/>
+        <v>1625</v>
       </c>
     </row>
     <row r="30">
@@ -12201,51 +12201,51 @@
       </c>
       <c r="J30" s="64">
         <f>IFERROR(J28/$V$28,0)</f>
-        <v/>
+        <v>0.0018461538461538461</v>
       </c>
       <c r="K30" s="64">
         <f>IFERROR(K28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L30" s="64">
         <f>IFERROR(L28/$V$28,0)</f>
-        <v/>
+        <v>0.024615384615384615</v>
       </c>
       <c r="M30" s="64">
         <f>IFERROR(M28/$V$28,0)</f>
-        <v/>
+        <v>0.07261538461538461</v>
       </c>
       <c r="N30" s="64">
         <f>IFERROR(N28/$V$28,0)</f>
-        <v/>
+        <v>0.04923076923076923</v>
       </c>
       <c r="O30" s="64">
         <f>IFERROR(O28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P30" s="64">
         <f>IFERROR(P28/$V$28,0)</f>
-        <v/>
+        <v>0.15753846153846154</v>
       </c>
       <c r="Q30" s="64">
         <f>IFERROR(Q28/$V$28,0)</f>
-        <v/>
+        <v>0.192</v>
       </c>
       <c r="R30" s="64">
         <f>IFERROR(R28/$V$28,0)</f>
-        <v/>
+        <v>0.2510769230769231</v>
       </c>
       <c r="S30" s="64">
         <f>IFERROR(S28/$V$28,0)</f>
-        <v/>
+        <v>0.2510769230769231</v>
       </c>
       <c r="T30" s="64">
         <f>IFERROR(T28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U30" s="64">
         <f>IFERROR(U28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -12260,9 +12260,9 @@
       <c r="E33" s="65" t="n"/>
       <c r="F33" s="65" t="n"/>
       <c r="G33" s="65" t="n"/>
-      <c r="H33" s="66">
+      <c r="H33" s="66" t="str">
         <f>" All Values in ( "&amp;C7&amp;" )"</f>
-        <v/>
+        <v> All Values in ( INR )</v>
       </c>
       <c r="I33" s="24" t="n"/>
       <c r="L33" s="67" t="inlineStr">
@@ -12358,12 +12358,12 @@
       <c r="P35" s="24" t="n"/>
       <c r="Q35" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>10865330</v>
       </c>
       <c r="R35" s="24" t="n"/>
       <c r="S35" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>10865330</v>
       </c>
     </row>
     <row r="36">
@@ -12374,24 +12374,24 @@
       </c>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="24" t="n"/>
-      <c r="D36" s="8">
+      <c r="D36" s="8" t="str">
         <f>C4</f>
-        <v/>
+        <v>India - R&amp;C</v>
       </c>
       <c r="F36" s="31">
         <f>V28</f>
-        <v/>
+        <v>1625</v>
       </c>
       <c r="G36" s="32">
         <f>D34-(SUM(G37:G40)+H41)</f>
-        <v/>
+        <v>4250000</v>
       </c>
       <c r="H36" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="30">
+      <c r="L36" s="30" t="str">
         <f>"Proposed Fee (Home Office)"&amp;" - "&amp;IF(D36=0,"",D36)</f>
-        <v/>
+        <v>Proposed Fee (Home Office) - India - R&amp;C</v>
       </c>
       <c r="M36" s="24" t="n"/>
       <c r="N36" s="24" t="n"/>
@@ -12399,12 +12399,12 @@
       <c r="P36" s="24" t="n"/>
       <c r="Q36" s="12">
         <f>G36</f>
-        <v/>
+        <v>4250000</v>
       </c>
       <c r="R36" s="73" t="n"/>
       <c r="S36" s="11">
         <f>S35*S39</f>
-        <v/>
+        <v>4250000</v>
       </c>
     </row>
     <row r="37">
@@ -12437,12 +12437,12 @@
       <c r="P37" s="24" t="n"/>
       <c r="Q37" s="11">
         <f>Q35-Q36</f>
-        <v/>
+        <v>6615330</v>
       </c>
       <c r="R37" s="24" t="n"/>
       <c r="S37" s="11">
         <f>S35-S36</f>
-        <v/>
+        <v>6615330</v>
       </c>
     </row>
     <row r="38">
@@ -12470,12 +12470,12 @@
       <c r="P38" s="24" t="n"/>
       <c r="Q38" s="74">
         <f>IFERROR(Q37/Q35,0)</f>
-        <v/>
+        <v>0.6088475913755036</v>
       </c>
       <c r="R38" s="24" t="n"/>
       <c r="S38" s="74">
         <f>1-S39</f>
-        <v/>
+        <v>0.6088475913755036</v>
       </c>
     </row>
     <row r="39">
@@ -12503,12 +12503,12 @@
       <c r="P39" s="24" t="n"/>
       <c r="Q39" s="75">
         <f>1-Q38</f>
-        <v/>
+        <v>0.39115240862449646</v>
       </c>
       <c r="R39" s="24" t="n"/>
       <c r="S39" s="76">
         <f>F43</f>
-        <v/>
+        <v>0.39115240862449646</v>
       </c>
     </row>
     <row r="40">
@@ -12543,15 +12543,15 @@
       <c r="E41" s="34" t="n"/>
       <c r="F41" s="78">
         <f>SUM(F36:F40)</f>
-        <v/>
+        <v>1625</v>
       </c>
       <c r="G41" s="79">
         <f>SUM(G36:G40)</f>
-        <v/>
+        <v>4250000</v>
       </c>
       <c r="H41" s="79">
         <f>SUM(H36:H40)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="F43" s="81">
         <f>IFERROR(G36/$AB$5,0)</f>
-        <v/>
+        <v>0.39115240862449646</v>
       </c>
       <c r="G43" s="24" t="n"/>
     </row>
@@ -12637,43 +12637,43 @@
       </c>
     </row>
     <row r="46">
-      <c r="K46" s="67">
+      <c r="K46" s="67" t="str">
         <f>C7</f>
-        <v/>
+        <v>INR</v>
       </c>
       <c r="L46" s="11">
         <f>G41</f>
-        <v/>
+        <v>4250000</v>
       </c>
       <c r="M46" s="10">
         <f>IFERROR(L46/F41,0)</f>
-        <v/>
+        <v>2615.3846153846152</v>
       </c>
       <c r="N46" s="11">
         <f>G36</f>
-        <v/>
+        <v>4250000</v>
       </c>
       <c r="O46" s="10">
         <f>IFERROR(N46/V28,0)</f>
-        <v/>
+        <v>2615.3846153846152</v>
       </c>
       <c r="P46" s="83">
         <f>IFERROR((T46-(N46*5%))/N46,0)</f>
-        <v/>
+        <v>0.2957430588235294</v>
       </c>
       <c r="Q46" s="84" t="n"/>
       <c r="R46" s="83">
         <f>IFERROR((L46-V46-(G41-G36)-(N46*5%))/L46,0)</f>
-        <v/>
+        <v>0.2957430588235294</v>
       </c>
       <c r="S46" s="84" t="n"/>
       <c r="T46" s="11">
         <f>IFERROR(N46-V46,0)</f>
-        <v/>
+        <v>1469408</v>
       </c>
       <c r="V46" s="11">
         <f>IFERROR($AB$6,0)</f>
-        <v/>
+        <v>2780592</v>
       </c>
     </row>
     <row r="48">
@@ -12785,15 +12785,15 @@
     <mergeCell ref="A33:G33"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId2"/>
+    <hyperlink ref="X4" ns1:id="rId1"/>
+    <hyperlink ref="X6" ns1:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00E57200"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12903,7 +12903,7 @@
       <c r="AA5" s="24" t="n"/>
       <c r="AB5" s="55">
         <f>SUMPRODUCT(J33:U33,Ratesheet!$B$23:$M$23)</f>
-        <v/>
+        <v>14999420</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -13009,7 +13009,7 @@
       <c r="AA6" s="24" t="n"/>
       <c r="AB6" s="55">
         <f>SUMPRODUCT(J33:U33,Ratesheet!$B$24:$M$24)</f>
-        <v/>
+        <v>3796320</v>
       </c>
     </row>
     <row r="7">
@@ -13058,7 +13058,7 @@
       <c r="AA7" s="24" t="n"/>
       <c r="AB7" s="10">
         <f>IFERROR(AB5/V33,0)</f>
-        <v/>
+        <v>6429.241320188598</v>
       </c>
     </row>
     <row r="8">
@@ -13118,7 +13118,7 @@
       <c r="U8" s="59" t="n"/>
       <c r="V8" s="60">
         <f>SUM(J8:U8)</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="Z8" s="30" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
       <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="10">
         <f>IFERROR(AB6/V33,0)</f>
-        <v/>
+        <v>1627.2267466780968</v>
       </c>
     </row>
     <row r="9">
@@ -13176,7 +13176,7 @@
       <c r="U9" s="59" t="n"/>
       <c r="V9" s="60">
         <f>SUM(J9:U9)</f>
-        <v/>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -13224,7 +13224,7 @@
       <c r="U10" s="59" t="n"/>
       <c r="V10" s="60">
         <f>SUM(J10:U10)</f>
-        <v/>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -13270,7 +13270,7 @@
       <c r="U11" s="59" t="n"/>
       <c r="V11" s="60">
         <f>SUM(J11:U11)</f>
-        <v/>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -13316,7 +13316,7 @@
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60">
         <f>SUM(J12:U12)</f>
-        <v/>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -13362,7 +13362,7 @@
       <c r="U13" s="59" t="n"/>
       <c r="V13" s="60">
         <f>SUM(J13:U13)</f>
-        <v/>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -13406,7 +13406,7 @@
       <c r="U14" s="59" t="n"/>
       <c r="V14" s="60">
         <f>SUM(J14:U14)</f>
-        <v/>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -13452,7 +13452,7 @@
       <c r="U15" s="59" t="n"/>
       <c r="V15" s="60">
         <f>SUM(J15:U15)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
     <row r="16">
@@ -13496,7 +13496,7 @@
       <c r="U16" s="59" t="n"/>
       <c r="V16" s="60">
         <f>SUM(J16:U16)</f>
-        <v/>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -13540,7 +13540,7 @@
       <c r="U17" s="59" t="n"/>
       <c r="V17" s="60">
         <f>SUM(J17:U17)</f>
-        <v/>
+        <v>98</v>
       </c>
     </row>
     <row r="18">
@@ -13584,7 +13584,7 @@
       <c r="U18" s="59" t="n"/>
       <c r="V18" s="60">
         <f>SUM(J18:U18)</f>
-        <v/>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
@@ -13628,7 +13628,7 @@
       <c r="U19" s="59" t="n"/>
       <c r="V19" s="60">
         <f>SUM(J19:U19)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -13674,7 +13674,7 @@
       <c r="U20" s="59" t="n"/>
       <c r="V20" s="60">
         <f>SUM(J20:U20)</f>
-        <v/>
+        <v>110</v>
       </c>
     </row>
     <row r="21">
@@ -13718,7 +13718,7 @@
       <c r="U21" s="59" t="n"/>
       <c r="V21" s="60">
         <f>SUM(J21:U21)</f>
-        <v/>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
@@ -13762,7 +13762,7 @@
       <c r="U22" s="59" t="n"/>
       <c r="V22" s="60">
         <f>SUM(J22:U22)</f>
-        <v/>
+        <v>124</v>
       </c>
     </row>
     <row r="23">
@@ -13806,7 +13806,7 @@
       <c r="U23" s="59" t="n"/>
       <c r="V23" s="60">
         <f>SUM(J23:U23)</f>
-        <v/>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
@@ -13850,7 +13850,7 @@
       <c r="U24" s="59" t="n"/>
       <c r="V24" s="60">
         <f>SUM(J24:U24)</f>
-        <v/>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
@@ -13894,7 +13894,7 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="60">
         <f>SUM(J25:U25)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -13938,7 +13938,7 @@
       <c r="U26" s="59" t="n"/>
       <c r="V26" s="60">
         <f>SUM(J26:U26)</f>
-        <v/>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
@@ -13984,7 +13984,7 @@
       <c r="U27" s="59" t="n"/>
       <c r="V27" s="60">
         <f>SUM(J27:U27)</f>
-        <v/>
+        <v>112</v>
       </c>
     </row>
     <row r="28">
@@ -14030,7 +14030,7 @@
       <c r="U28" s="59" t="n"/>
       <c r="V28" s="60">
         <f>SUM(J28:U28)</f>
-        <v/>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
@@ -14074,7 +14074,7 @@
       <c r="U29" s="59" t="n"/>
       <c r="V29" s="60">
         <f>SUM(J29:U29)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -14110,7 +14110,7 @@
       <c r="U30" s="59" t="n"/>
       <c r="V30" s="60">
         <f>SUM(J30:U30)</f>
-        <v/>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -14154,7 +14154,7 @@
       <c r="U31" s="59" t="n"/>
       <c r="V31" s="60">
         <f>SUM(J31:U31)</f>
-        <v/>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
@@ -14202,7 +14202,7 @@
       <c r="U32" s="59" t="n"/>
       <c r="V32" s="60">
         <f>SUM(J32:U32)</f>
-        <v/>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
@@ -14216,55 +14216,55 @@
       <c r="I33" s="34" t="n"/>
       <c r="J33" s="61">
         <f>SUM(J8:J32)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="K33" s="61">
         <f>SUM(K8:K32)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L33" s="61">
         <f>SUM(L8:L32)</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="M33" s="61">
         <f>SUM(M8:M32)</f>
-        <v/>
+        <v>158</v>
       </c>
       <c r="N33" s="61">
         <f>SUM(N8:N32)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="O33" s="61">
         <f>SUM(O8:O32)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P33" s="61">
         <f>SUM(P8:P32)</f>
-        <v/>
+        <v>344</v>
       </c>
       <c r="Q33" s="61">
         <f>SUM(Q8:Q32)</f>
-        <v/>
+        <v>440</v>
       </c>
       <c r="R33" s="61">
         <f>SUM(R8:R32)</f>
-        <v/>
+        <v>620</v>
       </c>
       <c r="S33" s="61">
         <f>SUM(S8:S32)</f>
-        <v/>
+        <v>620</v>
       </c>
       <c r="T33" s="61">
         <f>SUM(T8:T32)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U33" s="61">
         <f>SUM(U8:U32)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V33" s="62">
         <f>SUM(V8:V32)</f>
-        <v/>
+        <v>2333</v>
       </c>
     </row>
     <row r="35">
@@ -14275,51 +14275,51 @@
       </c>
       <c r="J35" s="64">
         <f>IFERROR(J33/$V$33,0)</f>
-        <v/>
+        <v>0.002571795970852979</v>
       </c>
       <c r="K35" s="64">
         <f>IFERROR(K33/$V$33,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L35" s="64">
         <f>IFERROR(L33/$V$33,0)</f>
-        <v/>
+        <v>0.01928846978139734</v>
       </c>
       <c r="M35" s="64">
         <f>IFERROR(M33/$V$33,0)</f>
-        <v/>
+        <v>0.06772396056579512</v>
       </c>
       <c r="N35" s="64">
         <f>IFERROR(N33/$V$33,0)</f>
-        <v/>
+        <v>0.042863266180882986</v>
       </c>
       <c r="O35" s="64">
         <f>IFERROR(O33/$V$33,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P35" s="64">
         <f>IFERROR(P33/$V$33,0)</f>
-        <v/>
+        <v>0.14744963566223745</v>
       </c>
       <c r="Q35" s="64">
         <f>IFERROR(Q33/$V$33,0)</f>
-        <v/>
+        <v>0.18859837119588513</v>
       </c>
       <c r="R35" s="64">
         <f>IFERROR(R33/$V$33,0)</f>
-        <v/>
+        <v>0.2657522503214745</v>
       </c>
       <c r="S35" s="64">
         <f>IFERROR(S33/$V$33,0)</f>
-        <v/>
+        <v>0.2657522503214745</v>
       </c>
       <c r="T35" s="64">
         <f>IFERROR(T33/$V$33,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U35" s="64">
         <f>IFERROR(U33/$V$33,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -14334,9 +14334,9 @@
       <c r="E38" s="65" t="n"/>
       <c r="F38" s="65" t="n"/>
       <c r="G38" s="65" t="n"/>
-      <c r="H38" s="66">
+      <c r="H38" s="66" t="str">
         <f>" All Values in ( "&amp;C7&amp;" )"</f>
-        <v/>
+        <v> All Values in ( INR )</v>
       </c>
       <c r="I38" s="24" t="n"/>
       <c r="L38" s="67" t="inlineStr">
@@ -14432,12 +14432,12 @@
       <c r="P40" s="24" t="n"/>
       <c r="Q40" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>14999420</v>
       </c>
       <c r="R40" s="24" t="n"/>
       <c r="S40" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>14999420</v>
       </c>
     </row>
     <row r="41">
@@ -14448,24 +14448,24 @@
       </c>
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="24" t="n"/>
-      <c r="D41" s="8">
+      <c r="D41" s="8" t="str">
         <f>C4</f>
-        <v/>
+        <v>India - R&amp;C</v>
       </c>
       <c r="F41" s="31">
         <f>V33</f>
-        <v/>
+        <v>2333</v>
       </c>
       <c r="G41" s="32">
         <f>D39-(SUM(G42:G45)+H46)</f>
-        <v/>
+        <v>5500000</v>
       </c>
       <c r="H41" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="30">
+      <c r="L41" s="30" t="str">
         <f>"Proposed Fee (Home Office)"&amp;" - "&amp;IF(D41=0,"",D41)</f>
-        <v/>
+        <v>Proposed Fee (Home Office) - India - R&amp;C</v>
       </c>
       <c r="M41" s="24" t="n"/>
       <c r="N41" s="24" t="n"/>
@@ -14473,12 +14473,12 @@
       <c r="P41" s="24" t="n"/>
       <c r="Q41" s="12">
         <f>G41</f>
-        <v/>
+        <v>5500000</v>
       </c>
       <c r="R41" s="73" t="n"/>
       <c r="S41" s="11">
         <f>S40*S44</f>
-        <v/>
+        <v>5500000</v>
       </c>
     </row>
     <row r="42">
@@ -14511,12 +14511,12 @@
       <c r="P42" s="24" t="n"/>
       <c r="Q42" s="11">
         <f>Q40-Q41</f>
-        <v/>
+        <v>9499420</v>
       </c>
       <c r="R42" s="24" t="n"/>
       <c r="S42" s="11">
         <f>S40-S41</f>
-        <v/>
+        <v>9499420</v>
       </c>
     </row>
     <row r="43">
@@ -14544,12 +14544,12 @@
       <c r="P43" s="24" t="n"/>
       <c r="Q43" s="74">
         <f>IFERROR(Q42/Q40,0)</f>
-        <v/>
+        <v>0.6333191550073269</v>
       </c>
       <c r="R43" s="24" t="n"/>
       <c r="S43" s="74">
         <f>1-S44</f>
-        <v/>
+        <v>0.6333191550073269</v>
       </c>
     </row>
     <row r="44">
@@ -14577,12 +14577,12 @@
       <c r="P44" s="24" t="n"/>
       <c r="Q44" s="75">
         <f>1-Q43</f>
-        <v/>
+        <v>0.36668084499267306</v>
       </c>
       <c r="R44" s="24" t="n"/>
       <c r="S44" s="76">
         <f>F48</f>
-        <v/>
+        <v>0.36668084499267306</v>
       </c>
     </row>
     <row r="45">
@@ -14617,15 +14617,15 @@
       <c r="E46" s="34" t="n"/>
       <c r="F46" s="78">
         <f>SUM(F41:F45)</f>
-        <v/>
+        <v>2333</v>
       </c>
       <c r="G46" s="79">
         <f>SUM(G41:G45)</f>
-        <v/>
+        <v>5500000</v>
       </c>
       <c r="H46" s="79">
         <f>SUM(H41:H45)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="F48" s="81">
         <f>IFERROR(G41/$AB$5,0)</f>
-        <v/>
+        <v>0.36668084499267306</v>
       </c>
       <c r="G48" s="24" t="n"/>
     </row>
@@ -14711,43 +14711,43 @@
       </c>
     </row>
     <row r="51">
-      <c r="K51" s="67">
+      <c r="K51" s="67" t="str">
         <f>C7</f>
-        <v/>
+        <v>INR</v>
       </c>
       <c r="L51" s="11">
         <f>G46</f>
-        <v/>
+        <v>5500000</v>
       </c>
       <c r="M51" s="10">
         <f>IFERROR(L51/F46,0)</f>
-        <v/>
+        <v>2357.479639948564</v>
       </c>
       <c r="N51" s="11">
         <f>G41</f>
-        <v/>
+        <v>5500000</v>
       </c>
       <c r="O51" s="10">
         <f>IFERROR(N51/V33,0)</f>
-        <v/>
+        <v>2357.479639948564</v>
       </c>
       <c r="P51" s="83">
         <f>IFERROR((T51-(N51*5%))/N51,0)</f>
-        <v/>
+        <v>0.25976</v>
       </c>
       <c r="Q51" s="84" t="n"/>
       <c r="R51" s="83">
         <f>IFERROR((L51-V51-(G46-G41)-(N51*5%))/L51,0)</f>
-        <v/>
+        <v>0.25976</v>
       </c>
       <c r="S51" s="84" t="n"/>
       <c r="T51" s="11">
         <f>IFERROR(N51-V51,0)</f>
-        <v/>
+        <v>1703680</v>
       </c>
       <c r="V51" s="11">
         <f>IFERROR($AB$6,0)</f>
-        <v/>
+        <v>3796320</v>
       </c>
     </row>
     <row r="53">
@@ -14864,15 +14864,15 @@
     <mergeCell ref="U6:U7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId2"/>
+    <hyperlink ref="X4" ns1:id="rId1"/>
+    <hyperlink ref="X6" ns1:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00E57200"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14982,7 +14982,7 @@
       <c r="AA5" s="24" t="n"/>
       <c r="AB5" s="55">
         <f>SUMPRODUCT(J28:U28,Ratesheet!$B$23:$M$23)</f>
-        <v/>
+        <v>8438810</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -15088,7 +15088,7 @@
       <c r="AA6" s="24" t="n"/>
       <c r="AB6" s="55">
         <f>SUMPRODUCT(J28:U28,Ratesheet!$B$24:$M$24)</f>
-        <v/>
+        <v>2152848</v>
       </c>
     </row>
     <row r="7">
@@ -15137,7 +15137,7 @@
       <c r="AA7" s="24" t="n"/>
       <c r="AB7" s="10">
         <f>IFERROR(AB5/V28,0)</f>
-        <v/>
+        <v>6556.961926961927</v>
       </c>
     </row>
     <row r="8">
@@ -15197,7 +15197,7 @@
       <c r="U8" s="59" t="n"/>
       <c r="V8" s="60">
         <f>SUM(J8:U8)</f>
-        <v/>
+        <v>63</v>
       </c>
       <c r="Z8" s="30" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
       <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="10">
         <f>IFERROR(AB6/V28,0)</f>
-        <v/>
+        <v>1672.7645687645688</v>
       </c>
     </row>
     <row r="9">
@@ -15255,7 +15255,7 @@
       <c r="U9" s="59" t="n"/>
       <c r="V9" s="60">
         <f>SUM(J9:U9)</f>
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -15301,7 +15301,7 @@
       <c r="U10" s="59" t="n"/>
       <c r="V10" s="60">
         <f>SUM(J10:U10)</f>
-        <v/>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -15347,7 +15347,7 @@
       <c r="U11" s="59" t="n"/>
       <c r="V11" s="60">
         <f>SUM(J11:U11)</f>
-        <v/>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -15393,7 +15393,7 @@
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60">
         <f>SUM(J12:U12)</f>
-        <v/>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -15439,7 +15439,7 @@
       <c r="U13" s="59" t="n"/>
       <c r="V13" s="60">
         <f>SUM(J13:U13)</f>
-        <v/>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -15485,7 +15485,7 @@
       <c r="U14" s="59" t="n"/>
       <c r="V14" s="60">
         <f>SUM(J14:U14)</f>
-        <v/>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -15529,7 +15529,7 @@
       <c r="U15" s="59" t="n"/>
       <c r="V15" s="60">
         <f>SUM(J15:U15)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -15573,7 +15573,7 @@
       <c r="U16" s="59" t="n"/>
       <c r="V16" s="60">
         <f>SUM(J16:U16)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
@@ -15617,7 +15617,7 @@
       <c r="U17" s="59" t="n"/>
       <c r="V17" s="60">
         <f>SUM(J17:U17)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -15661,7 +15661,7 @@
       <c r="U18" s="59" t="n"/>
       <c r="V18" s="60">
         <f>SUM(J18:U18)</f>
-        <v/>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
@@ -15705,7 +15705,7 @@
       <c r="U19" s="59" t="n"/>
       <c r="V19" s="60">
         <f>SUM(J19:U19)</f>
-        <v/>
+        <v>86</v>
       </c>
     </row>
     <row r="20">
@@ -15749,7 +15749,7 @@
       <c r="U20" s="59" t="n"/>
       <c r="V20" s="60">
         <f>SUM(J20:U20)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
@@ -15793,7 +15793,7 @@
       <c r="U21" s="59" t="n"/>
       <c r="V21" s="60">
         <f>SUM(J21:U21)</f>
-        <v/>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -15839,7 +15839,7 @@
       <c r="U22" s="59" t="n"/>
       <c r="V22" s="60">
         <f>SUM(J22:U22)</f>
-        <v/>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
@@ -15885,7 +15885,7 @@
       <c r="U23" s="59" t="n"/>
       <c r="V23" s="60">
         <f>SUM(J23:U23)</f>
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
@@ -15929,7 +15929,7 @@
       <c r="U24" s="59" t="n"/>
       <c r="V24" s="60">
         <f>SUM(J24:U24)</f>
-        <v/>
+        <v>42</v>
       </c>
     </row>
     <row r="25">
@@ -15965,7 +15965,7 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="60">
         <f>SUM(J25:U25)</f>
-        <v/>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
@@ -16009,7 +16009,7 @@
       <c r="U26" s="59" t="n"/>
       <c r="V26" s="60">
         <f>SUM(J26:U26)</f>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -16057,7 +16057,7 @@
       <c r="U27" s="59" t="n"/>
       <c r="V27" s="60">
         <f>SUM(J27:U27)</f>
-        <v/>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -16071,55 +16071,55 @@
       <c r="I28" s="34" t="n"/>
       <c r="J28" s="61">
         <f>SUM(J8:J27)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="K28" s="61">
         <f>SUM(K8:K27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L28" s="61">
         <f>SUM(L8:L27)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="M28" s="61">
         <f>SUM(M8:M27)</f>
-        <v/>
+        <v>92</v>
       </c>
       <c r="N28" s="61">
         <f>SUM(N8:N27)</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="O28" s="61">
         <f>SUM(O8:O27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P28" s="61">
         <f>SUM(P8:P27)</f>
-        <v/>
+        <v>184</v>
       </c>
       <c r="Q28" s="61">
         <f>SUM(Q8:Q27)</f>
-        <v/>
+        <v>256</v>
       </c>
       <c r="R28" s="61">
         <f>SUM(R8:R27)</f>
-        <v/>
+        <v>332</v>
       </c>
       <c r="S28" s="61">
         <f>SUM(S8:S27)</f>
-        <v/>
+        <v>332</v>
       </c>
       <c r="T28" s="61">
         <f>SUM(T8:T27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U28" s="61">
         <f>SUM(U8:U27)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V28" s="62">
         <f>SUM(V8:V27)</f>
-        <v/>
+        <v>1287</v>
       </c>
     </row>
     <row r="30">
@@ -16130,51 +16130,51 @@
       </c>
       <c r="J30" s="64">
         <f>IFERROR(J28/$V$28,0)</f>
-        <v/>
+        <v>0.002331002331002331</v>
       </c>
       <c r="K30" s="64">
         <f>IFERROR(K28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L30" s="64">
         <f>IFERROR(L28/$V$28,0)</f>
-        <v/>
+        <v>0.021756021756021756</v>
       </c>
       <c r="M30" s="64">
         <f>IFERROR(M28/$V$28,0)</f>
-        <v/>
+        <v>0.07148407148407149</v>
       </c>
       <c r="N30" s="64">
         <f>IFERROR(N28/$V$28,0)</f>
-        <v/>
+        <v>0.046620046620046623</v>
       </c>
       <c r="O30" s="64">
         <f>IFERROR(O28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P30" s="64">
         <f>IFERROR(P28/$V$28,0)</f>
-        <v/>
+        <v>0.14296814296814297</v>
       </c>
       <c r="Q30" s="64">
         <f>IFERROR(Q28/$V$28,0)</f>
-        <v/>
+        <v>0.1989121989121989</v>
       </c>
       <c r="R30" s="64">
         <f>IFERROR(R28/$V$28,0)</f>
-        <v/>
+        <v>0.257964257964258</v>
       </c>
       <c r="S30" s="64">
         <f>IFERROR(S28/$V$28,0)</f>
-        <v/>
+        <v>0.257964257964258</v>
       </c>
       <c r="T30" s="64">
         <f>IFERROR(T28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U30" s="64">
         <f>IFERROR(U28/$V$28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -16189,9 +16189,9 @@
       <c r="E33" s="65" t="n"/>
       <c r="F33" s="65" t="n"/>
       <c r="G33" s="65" t="n"/>
-      <c r="H33" s="66">
+      <c r="H33" s="66" t="str">
         <f>" All Values in ( "&amp;C7&amp;" )"</f>
-        <v/>
+        <v> All Values in ( INR )</v>
       </c>
       <c r="I33" s="24" t="n"/>
       <c r="L33" s="67" t="inlineStr">
@@ -16287,12 +16287,12 @@
       <c r="P35" s="24" t="n"/>
       <c r="Q35" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>8438810</v>
       </c>
       <c r="R35" s="24" t="n"/>
       <c r="S35" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>8438810</v>
       </c>
     </row>
     <row r="36">
@@ -16303,24 +16303,24 @@
       </c>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="24" t="n"/>
-      <c r="D36" s="8">
+      <c r="D36" s="8" t="str">
         <f>C4</f>
-        <v/>
+        <v>India - R&amp;C</v>
       </c>
       <c r="F36" s="31">
         <f>V28</f>
-        <v/>
+        <v>1287</v>
       </c>
       <c r="G36" s="32">
         <f>D34-(SUM(G37:G40)+H41)</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="H36" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="30">
+      <c r="L36" s="30" t="str">
         <f>"Proposed Fee (Home Office)"&amp;" - "&amp;IF(D36=0,"",D36)</f>
-        <v/>
+        <v>Proposed Fee (Home Office) - India - R&amp;C</v>
       </c>
       <c r="M36" s="24" t="n"/>
       <c r="N36" s="24" t="n"/>
@@ -16328,12 +16328,12 @@
       <c r="P36" s="24" t="n"/>
       <c r="Q36" s="12">
         <f>G36</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="R36" s="73" t="n"/>
       <c r="S36" s="11">
         <f>S35*S39</f>
-        <v/>
+        <v>3250000</v>
       </c>
     </row>
     <row r="37">
@@ -16366,12 +16366,12 @@
       <c r="P37" s="24" t="n"/>
       <c r="Q37" s="11">
         <f>Q35-Q36</f>
-        <v/>
+        <v>5188810</v>
       </c>
       <c r="R37" s="24" t="n"/>
       <c r="S37" s="11">
         <f>S35-S36</f>
-        <v/>
+        <v>5188810</v>
       </c>
     </row>
     <row r="38">
@@ -16399,12 +16399,12 @@
       <c r="P38" s="24" t="n"/>
       <c r="Q38" s="74">
         <f>IFERROR(Q37/Q35,0)</f>
-        <v/>
+        <v>0.6148746090977283</v>
       </c>
       <c r="R38" s="24" t="n"/>
       <c r="S38" s="74">
         <f>1-S39</f>
-        <v/>
+        <v>0.6148746090977282</v>
       </c>
     </row>
     <row r="39">
@@ -16432,12 +16432,12 @@
       <c r="P39" s="24" t="n"/>
       <c r="Q39" s="75">
         <f>1-Q38</f>
-        <v/>
+        <v>0.38512539090227177</v>
       </c>
       <c r="R39" s="24" t="n"/>
       <c r="S39" s="76">
         <f>F43</f>
-        <v/>
+        <v>0.38512539090227177</v>
       </c>
     </row>
     <row r="40">
@@ -16472,15 +16472,15 @@
       <c r="E41" s="34" t="n"/>
       <c r="F41" s="78">
         <f>SUM(F36:F40)</f>
-        <v/>
+        <v>1287</v>
       </c>
       <c r="G41" s="79">
         <f>SUM(G36:G40)</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="H41" s="79">
         <f>SUM(H36:H40)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="F43" s="81">
         <f>IFERROR(G36/$AB$5,0)</f>
-        <v/>
+        <v>0.38512539090227177</v>
       </c>
       <c r="G43" s="24" t="n"/>
     </row>
@@ -16566,43 +16566,43 @@
       </c>
     </row>
     <row r="46">
-      <c r="K46" s="67">
+      <c r="K46" s="67" t="str">
         <f>C7</f>
-        <v/>
+        <v>INR</v>
       </c>
       <c r="L46" s="11">
         <f>G41</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="M46" s="10">
         <f>IFERROR(L46/F41,0)</f>
-        <v/>
+        <v>2525.252525252525</v>
       </c>
       <c r="N46" s="11">
         <f>G36</f>
-        <v/>
+        <v>3250000</v>
       </c>
       <c r="O46" s="10">
         <f>IFERROR(N46/V28,0)</f>
-        <v/>
+        <v>2525.252525252525</v>
       </c>
       <c r="P46" s="83">
         <f>IFERROR((T46-(N46*5%))/N46,0)</f>
-        <v/>
+        <v>0.28758523076923076</v>
       </c>
       <c r="Q46" s="84" t="n"/>
       <c r="R46" s="83">
         <f>IFERROR((L46-V46-(G41-G36)-(N46*5%))/L46,0)</f>
-        <v/>
+        <v>0.28758523076923076</v>
       </c>
       <c r="S46" s="84" t="n"/>
       <c r="T46" s="11">
         <f>IFERROR(N46-V46,0)</f>
-        <v/>
+        <v>1097152</v>
       </c>
       <c r="V46" s="11">
         <f>IFERROR($AB$6,0)</f>
-        <v/>
+        <v>2152848</v>
       </c>
     </row>
     <row r="48">
@@ -16714,15 +16714,15 @@
     <mergeCell ref="A33:G33"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId2"/>
+    <hyperlink ref="X4" ns1:id="rId1"/>
+    <hyperlink ref="X6" ns1:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00E57200"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16832,7 +16832,7 @@
       <c r="AA5" s="24" t="n"/>
       <c r="AB5" s="55">
         <f>SUMPRODUCT(J34:U34,Ratesheet!$B$23:$M$23)</f>
-        <v/>
+        <v>16830130</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -16938,7 +16938,7 @@
       <c r="AA6" s="24" t="n"/>
       <c r="AB6" s="55">
         <f>SUMPRODUCT(J34:U34,Ratesheet!$B$24:$M$24)</f>
-        <v/>
+        <v>4322544</v>
       </c>
     </row>
     <row r="7">
@@ -16987,7 +16987,7 @@
       <c r="AA7" s="24" t="n"/>
       <c r="AB7" s="10">
         <f>IFERROR(AB5/V34,0)</f>
-        <v/>
+        <v>6620.822187254131</v>
       </c>
     </row>
     <row r="8">
@@ -17047,7 +17047,7 @@
       <c r="U8" s="59" t="n"/>
       <c r="V8" s="60">
         <f>SUM(J8:U8)</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="Z8" s="30" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
       <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="10">
         <f>IFERROR(AB6/V34,0)</f>
-        <v/>
+        <v>1700.4500393391031</v>
       </c>
     </row>
     <row r="9">
@@ -17105,7 +17105,7 @@
       <c r="U9" s="59" t="n"/>
       <c r="V9" s="60">
         <f>SUM(J9:U9)</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -17151,7 +17151,7 @@
       <c r="U10" s="59" t="n"/>
       <c r="V10" s="60">
         <f>SUM(J10:U10)</f>
-        <v/>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -17197,7 +17197,7 @@
       <c r="U11" s="59" t="n"/>
       <c r="V11" s="60">
         <f>SUM(J11:U11)</f>
-        <v/>
+        <v>148</v>
       </c>
     </row>
     <row r="12">
@@ -17243,7 +17243,7 @@
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60">
         <f>SUM(J12:U12)</f>
-        <v/>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
@@ -17287,7 +17287,7 @@
       <c r="U13" s="59" t="n"/>
       <c r="V13" s="60">
         <f>SUM(J13:U13)</f>
-        <v/>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -17333,7 +17333,7 @@
       <c r="U14" s="59" t="n"/>
       <c r="V14" s="60">
         <f>SUM(J14:U14)</f>
-        <v/>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -17379,7 +17379,7 @@
       <c r="U15" s="59" t="n"/>
       <c r="V15" s="60">
         <f>SUM(J15:U15)</f>
-        <v/>
+        <v>132</v>
       </c>
     </row>
     <row r="16">
@@ -17425,7 +17425,7 @@
       <c r="U16" s="59" t="n"/>
       <c r="V16" s="60">
         <f>SUM(J16:U16)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
@@ -17471,7 +17471,7 @@
       <c r="U17" s="59" t="n"/>
       <c r="V17" s="60">
         <f>SUM(J17:U17)</f>
-        <v/>
+        <v>102</v>
       </c>
     </row>
     <row r="18">
@@ -17517,7 +17517,7 @@
       <c r="U18" s="59" t="n"/>
       <c r="V18" s="60">
         <f>SUM(J18:U18)</f>
-        <v/>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -17563,7 +17563,7 @@
       <c r="U19" s="59" t="n"/>
       <c r="V19" s="60">
         <f>SUM(J19:U19)</f>
-        <v/>
+        <v>122</v>
       </c>
     </row>
     <row r="20">
@@ -17609,7 +17609,7 @@
       <c r="U20" s="59" t="n"/>
       <c r="V20" s="60">
         <f>SUM(J20:U20)</f>
-        <v/>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
@@ -17655,7 +17655,7 @@
       <c r="U21" s="59" t="n"/>
       <c r="V21" s="60">
         <f>SUM(J21:U21)</f>
-        <v/>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
@@ -17701,7 +17701,7 @@
       <c r="U22" s="59" t="n"/>
       <c r="V22" s="60">
         <f>SUM(J22:U22)</f>
-        <v/>
+        <v>92</v>
       </c>
     </row>
     <row r="23">
@@ -17745,7 +17745,7 @@
       <c r="U23" s="59" t="n"/>
       <c r="V23" s="60">
         <f>SUM(J23:U23)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -17789,7 +17789,7 @@
       <c r="U24" s="59" t="n"/>
       <c r="V24" s="60">
         <f>SUM(J24:U24)</f>
-        <v/>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
@@ -17833,7 +17833,7 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="60">
         <f>SUM(J25:U25)</f>
-        <v/>
+        <v>124</v>
       </c>
     </row>
     <row r="26">
@@ -17877,7 +17877,7 @@
       <c r="U26" s="59" t="n"/>
       <c r="V26" s="60">
         <f>SUM(J26:U26)</f>
-        <v/>
+        <v>86</v>
       </c>
     </row>
     <row r="27">
@@ -17921,7 +17921,7 @@
       <c r="U27" s="59" t="n"/>
       <c r="V27" s="60">
         <f>SUM(J27:U27)</f>
-        <v/>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
@@ -17967,7 +17967,7 @@
       <c r="U28" s="59" t="n"/>
       <c r="V28" s="60">
         <f>SUM(J28:U28)</f>
-        <v/>
+        <v>114</v>
       </c>
     </row>
     <row r="29">
@@ -18013,7 +18013,7 @@
       <c r="U29" s="59" t="n"/>
       <c r="V29" s="60">
         <f>SUM(J29:U29)</f>
-        <v/>
+        <v>73</v>
       </c>
     </row>
     <row r="30">
@@ -18057,7 +18057,7 @@
       <c r="U30" s="59" t="n"/>
       <c r="V30" s="60">
         <f>SUM(J30:U30)</f>
-        <v/>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
@@ -18093,7 +18093,7 @@
       <c r="U31" s="59" t="n"/>
       <c r="V31" s="60">
         <f>SUM(J31:U31)</f>
-        <v/>
+        <v>110</v>
       </c>
     </row>
     <row r="32">
@@ -18137,7 +18137,7 @@
       <c r="U32" s="59" t="n"/>
       <c r="V32" s="60">
         <f>SUM(J32:U32)</f>
-        <v/>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -18185,7 +18185,7 @@
       <c r="U33" s="59" t="n"/>
       <c r="V33" s="60">
         <f>SUM(J33:U33)</f>
-        <v/>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -18199,55 +18199,55 @@
       <c r="I34" s="34" t="n"/>
       <c r="J34" s="61">
         <f>SUM(J8:J33)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K34" s="61">
         <f>SUM(K8:K33)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L34" s="61">
         <f>SUM(L8:L33)</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="M34" s="61">
         <f>SUM(M8:M33)</f>
-        <v/>
+        <v>186</v>
       </c>
       <c r="N34" s="61">
         <f>SUM(N8:N33)</f>
-        <v/>
+        <v>110</v>
       </c>
       <c r="O34" s="61">
         <f>SUM(O8:O33)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P34" s="61">
         <f>SUM(P8:P33)</f>
-        <v/>
+        <v>384</v>
       </c>
       <c r="Q34" s="61">
         <f>SUM(Q8:Q33)</f>
-        <v/>
+        <v>480</v>
       </c>
       <c r="R34" s="61">
         <f>SUM(R8:R33)</f>
-        <v/>
+        <v>656</v>
       </c>
       <c r="S34" s="61">
         <f>SUM(S8:S33)</f>
-        <v/>
+        <v>656</v>
       </c>
       <c r="T34" s="61">
         <f>SUM(T8:T33)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U34" s="61">
         <f>SUM(U8:U33)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V34" s="62">
         <f>SUM(V8:V33)</f>
-        <v/>
+        <v>2542</v>
       </c>
     </row>
     <row r="36">
@@ -18258,51 +18258,51 @@
       </c>
       <c r="J36" s="64">
         <f>IFERROR(J34/$V$34,0)</f>
-        <v/>
+        <v>0.001966955153422502</v>
       </c>
       <c r="K36" s="64">
         <f>IFERROR(K34/$V$34,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L36" s="64">
         <f>IFERROR(L34/$V$34,0)</f>
-        <v/>
+        <v>0.025570416994492525</v>
       </c>
       <c r="M36" s="64">
         <f>IFERROR(M34/$V$34,0)</f>
-        <v/>
+        <v>0.07317073170731707</v>
       </c>
       <c r="N36" s="64">
         <f>IFERROR(N34/$V$34,0)</f>
-        <v/>
+        <v>0.043273013375295044</v>
       </c>
       <c r="O36" s="64">
         <f>IFERROR(O34/$V$34,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P36" s="64">
         <f>IFERROR(P34/$V$34,0)</f>
-        <v/>
+        <v>0.15106215578284815</v>
       </c>
       <c r="Q36" s="64">
         <f>IFERROR(Q34/$V$34,0)</f>
-        <v/>
+        <v>0.1888276947285602</v>
       </c>
       <c r="R36" s="64">
         <f>IFERROR(R34/$V$34,0)</f>
-        <v/>
+        <v>0.25806451612903225</v>
       </c>
       <c r="S36" s="64">
         <f>IFERROR(S34/$V$34,0)</f>
-        <v/>
+        <v>0.25806451612903225</v>
       </c>
       <c r="T36" s="64">
         <f>IFERROR(T34/$V$34,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U36" s="64">
         <f>IFERROR(U34/$V$34,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -18317,9 +18317,9 @@
       <c r="E39" s="65" t="n"/>
       <c r="F39" s="65" t="n"/>
       <c r="G39" s="65" t="n"/>
-      <c r="H39" s="66">
+      <c r="H39" s="66" t="str">
         <f>" All Values in ( "&amp;C7&amp;" )"</f>
-        <v/>
+        <v> All Values in ( INR )</v>
       </c>
       <c r="I39" s="24" t="n"/>
       <c r="L39" s="67" t="inlineStr">
@@ -18415,12 +18415,12 @@
       <c r="P41" s="24" t="n"/>
       <c r="Q41" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>16830130</v>
       </c>
       <c r="R41" s="24" t="n"/>
       <c r="S41" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>16830130</v>
       </c>
     </row>
     <row r="42">
@@ -18431,24 +18431,24 @@
       </c>
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="24" t="n"/>
-      <c r="D42" s="8">
+      <c r="D42" s="8" t="str">
         <f>C4</f>
-        <v/>
+        <v>India - R&amp;C</v>
       </c>
       <c r="F42" s="31">
         <f>V34</f>
-        <v/>
+        <v>2542</v>
       </c>
       <c r="G42" s="32">
         <f>D40-(SUM(G43:G46)+H47)</f>
-        <v/>
+        <v>6750000</v>
       </c>
       <c r="H42" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="30">
+      <c r="L42" s="30" t="str">
         <f>"Proposed Fee (Home Office)"&amp;" - "&amp;IF(D42=0,"",D42)</f>
-        <v/>
+        <v>Proposed Fee (Home Office) - India - R&amp;C</v>
       </c>
       <c r="M42" s="24" t="n"/>
       <c r="N42" s="24" t="n"/>
@@ -18456,12 +18456,12 @@
       <c r="P42" s="24" t="n"/>
       <c r="Q42" s="12">
         <f>G42</f>
-        <v/>
+        <v>6750000</v>
       </c>
       <c r="R42" s="73" t="n"/>
       <c r="S42" s="11">
         <f>S41*S45</f>
-        <v/>
+        <v>6750000</v>
       </c>
     </row>
     <row r="43">
@@ -18494,12 +18494,12 @@
       <c r="P43" s="24" t="n"/>
       <c r="Q43" s="11">
         <f>Q41-Q42</f>
-        <v/>
+        <v>10080130</v>
       </c>
       <c r="R43" s="24" t="n"/>
       <c r="S43" s="11">
         <f>S41-S42</f>
-        <v/>
+        <v>10080130</v>
       </c>
     </row>
     <row r="44">
@@ -18527,12 +18527,12 @@
       <c r="P44" s="24" t="n"/>
       <c r="Q44" s="74">
         <f>IFERROR(Q43/Q41,0)</f>
-        <v/>
+        <v>0.598933579241515</v>
       </c>
       <c r="R44" s="24" t="n"/>
       <c r="S44" s="74">
         <f>1-S45</f>
-        <v/>
+        <v>0.5989335792415151</v>
       </c>
     </row>
     <row r="45">
@@ -18560,12 +18560,12 @@
       <c r="P45" s="24" t="n"/>
       <c r="Q45" s="75">
         <f>1-Q44</f>
-        <v/>
+        <v>0.4010664207584849</v>
       </c>
       <c r="R45" s="24" t="n"/>
       <c r="S45" s="76">
         <f>F49</f>
-        <v/>
+        <v>0.4010664207584849</v>
       </c>
     </row>
     <row r="46">
@@ -18600,15 +18600,15 @@
       <c r="E47" s="34" t="n"/>
       <c r="F47" s="78">
         <f>SUM(F42:F46)</f>
-        <v/>
+        <v>2542</v>
       </c>
       <c r="G47" s="79">
         <f>SUM(G42:G46)</f>
-        <v/>
+        <v>6750000</v>
       </c>
       <c r="H47" s="79">
         <f>SUM(H42:H46)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="F49" s="81">
         <f>IFERROR(G42/$AB$5,0)</f>
-        <v/>
+        <v>0.4010664207584849</v>
       </c>
       <c r="G49" s="24" t="n"/>
     </row>
@@ -18694,43 +18694,43 @@
       </c>
     </row>
     <row r="52">
-      <c r="K52" s="67">
+      <c r="K52" s="67" t="str">
         <f>C7</f>
-        <v/>
+        <v>INR</v>
       </c>
       <c r="L52" s="11">
         <f>G47</f>
-        <v/>
+        <v>6750000</v>
       </c>
       <c r="M52" s="10">
         <f>IFERROR(L52/F47,0)</f>
-        <v/>
+        <v>2655.3894571203778</v>
       </c>
       <c r="N52" s="11">
         <f>G42</f>
-        <v/>
+        <v>6750000</v>
       </c>
       <c r="O52" s="10">
         <f>IFERROR(N52/V34,0)</f>
-        <v/>
+        <v>2655.3894571203778</v>
       </c>
       <c r="P52" s="83">
         <f>IFERROR((T52-(N52*5%))/N52,0)</f>
-        <v/>
+        <v>0.3096231111111111</v>
       </c>
       <c r="Q52" s="84" t="n"/>
       <c r="R52" s="83">
         <f>IFERROR((L52-V52-(G47-G42)-(N52*5%))/L52,0)</f>
-        <v/>
+        <v>0.3096231111111111</v>
       </c>
       <c r="S52" s="84" t="n"/>
       <c r="T52" s="11">
         <f>IFERROR(N52-V52,0)</f>
-        <v/>
+        <v>2427456</v>
       </c>
       <c r="V52" s="11">
         <f>IFERROR($AB$6,0)</f>
-        <v/>
+        <v>4322544</v>
       </c>
     </row>
     <row r="54">
@@ -18848,15 +18848,15 @@
     <mergeCell ref="U6:U7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId2"/>
+    <hyperlink ref="X4" ns1:id="rId1"/>
+    <hyperlink ref="X6" ns1:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="00E57200"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18966,7 +18966,7 @@
       <c r="AA5" s="24" t="n"/>
       <c r="AB5" s="55">
         <f>SUMPRODUCT(J31:U31,Ratesheet!$B$23:$M$23)</f>
-        <v/>
+        <v>13756660</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -19072,7 +19072,7 @@
       <c r="AA6" s="24" t="n"/>
       <c r="AB6" s="55">
         <f>SUMPRODUCT(J31:U31,Ratesheet!$B$24:$M$24)</f>
-        <v/>
+        <v>3493176</v>
       </c>
     </row>
     <row r="7">
@@ -19121,7 +19121,7 @@
       <c r="AA7" s="24" t="n"/>
       <c r="AB7" s="10">
         <f>IFERROR(AB5/V31,0)</f>
-        <v/>
+        <v>6449.442100328176</v>
       </c>
     </row>
     <row r="8">
@@ -19181,7 +19181,7 @@
       <c r="U8" s="59" t="n"/>
       <c r="V8" s="60">
         <f>SUM(J8:U8)</f>
-        <v/>
+        <v>94</v>
       </c>
       <c r="Z8" s="30" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
       <c r="AA8" s="24" t="n"/>
       <c r="AB8" s="10">
         <f>IFERROR(AB6/V31,0)</f>
-        <v/>
+        <v>1637.6821378340367</v>
       </c>
     </row>
     <row r="9">
@@ -19239,7 +19239,7 @@
       <c r="U9" s="59" t="n"/>
       <c r="V9" s="60">
         <f>SUM(J9:U9)</f>
-        <v/>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -19287,7 +19287,7 @@
       <c r="U10" s="59" t="n"/>
       <c r="V10" s="60">
         <f>SUM(J10:U10)</f>
-        <v/>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -19333,7 +19333,7 @@
       <c r="U11" s="59" t="n"/>
       <c r="V11" s="60">
         <f>SUM(J11:U11)</f>
-        <v/>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
@@ -19379,7 +19379,7 @@
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60">
         <f>SUM(J12:U12)</f>
-        <v/>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -19425,7 +19425,7 @@
       <c r="U13" s="59" t="n"/>
       <c r="V13" s="60">
         <f>SUM(J13:U13)</f>
-        <v/>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -19469,7 +19469,7 @@
       <c r="U14" s="59" t="n"/>
       <c r="V14" s="60">
         <f>SUM(J14:U14)</f>
-        <v/>
+        <v>106</v>
       </c>
     </row>
     <row r="15">
@@ -19515,7 +19515,7 @@
       <c r="U15" s="59" t="n"/>
       <c r="V15" s="60">
         <f>SUM(J15:U15)</f>
-        <v/>
+        <v>108</v>
       </c>
     </row>
     <row r="16">
@@ -19559,7 +19559,7 @@
       <c r="U16" s="59" t="n"/>
       <c r="V16" s="60">
         <f>SUM(J16:U16)</f>
-        <v/>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -19603,7 +19603,7 @@
       <c r="U17" s="59" t="n"/>
       <c r="V17" s="60">
         <f>SUM(J17:U17)</f>
-        <v/>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
@@ -19649,7 +19649,7 @@
       <c r="U18" s="59" t="n"/>
       <c r="V18" s="60">
         <f>SUM(J18:U18)</f>
-        <v/>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -19695,7 +19695,7 @@
       <c r="U19" s="59" t="n"/>
       <c r="V19" s="60">
         <f>SUM(J19:U19)</f>
-        <v/>
+        <v>108</v>
       </c>
     </row>
     <row r="20">
@@ -19741,7 +19741,7 @@
       <c r="U20" s="59" t="n"/>
       <c r="V20" s="60">
         <f>SUM(J20:U20)</f>
-        <v/>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -19785,7 +19785,7 @@
       <c r="U21" s="59" t="n"/>
       <c r="V21" s="60">
         <f>SUM(J21:U21)</f>
-        <v/>
+        <v>136</v>
       </c>
     </row>
     <row r="22">
@@ -19829,7 +19829,7 @@
       <c r="U22" s="59" t="n"/>
       <c r="V22" s="60">
         <f>SUM(J22:U22)</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
@@ -19873,7 +19873,7 @@
       <c r="U23" s="59" t="n"/>
       <c r="V23" s="60">
         <f>SUM(J23:U23)</f>
-        <v/>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
@@ -19917,7 +19917,7 @@
       <c r="U24" s="59" t="n"/>
       <c r="V24" s="60">
         <f>SUM(J24:U24)</f>
-        <v/>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
@@ -19963,7 +19963,7 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="60">
         <f>SUM(J25:U25)</f>
-        <v/>
+        <v>112</v>
       </c>
     </row>
     <row r="26">
@@ -20009,7 +20009,7 @@
       <c r="U26" s="59" t="n"/>
       <c r="V26" s="60">
         <f>SUM(J26:U26)</f>
-        <v/>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
@@ -20053,7 +20053,7 @@
       <c r="U27" s="59" t="n"/>
       <c r="V27" s="60">
         <f>SUM(J27:U27)</f>
-        <v/>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
@@ -20089,7 +20089,7 @@
       <c r="U28" s="59" t="n"/>
       <c r="V28" s="60">
         <f>SUM(J28:U28)</f>
-        <v/>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -20133,7 +20133,7 @@
       <c r="U29" s="59" t="n"/>
       <c r="V29" s="60">
         <f>SUM(J29:U29)</f>
-        <v/>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
@@ -20181,7 +20181,7 @@
       <c r="U30" s="59" t="n"/>
       <c r="V30" s="60">
         <f>SUM(J30:U30)</f>
-        <v/>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
@@ -20195,55 +20195,55 @@
       <c r="I31" s="34" t="n"/>
       <c r="J31" s="61">
         <f>SUM(J8:J30)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="K31" s="61">
         <f>SUM(K8:K30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L31" s="61">
         <f>SUM(L8:L30)</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="M31" s="61">
         <f>SUM(M8:M30)</f>
-        <v/>
+        <v>134</v>
       </c>
       <c r="N31" s="61">
         <f>SUM(N8:N30)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="O31" s="61">
         <f>SUM(O8:O30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P31" s="61">
         <f>SUM(P8:P30)</f>
-        <v/>
+        <v>316</v>
       </c>
       <c r="Q31" s="61">
         <f>SUM(Q8:Q30)</f>
-        <v/>
+        <v>404</v>
       </c>
       <c r="R31" s="61">
         <f>SUM(R8:R30)</f>
-        <v/>
+        <v>564</v>
       </c>
       <c r="S31" s="61">
         <f>SUM(S8:S30)</f>
-        <v/>
+        <v>564</v>
       </c>
       <c r="T31" s="61">
         <f>SUM(T8:T30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U31" s="61">
         <f>SUM(U8:U30)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="V31" s="62">
         <f>SUM(V8:V30)</f>
-        <v/>
+        <v>2133</v>
       </c>
     </row>
     <row r="33">
@@ -20254,51 +20254,51 @@
       </c>
       <c r="J33" s="64">
         <f>IFERROR(J31/$V$31,0)</f>
-        <v/>
+        <v>0.0028129395218002813</v>
       </c>
       <c r="K33" s="64">
         <f>IFERROR(K31/$V$31,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L33" s="64">
         <f>IFERROR(L31/$V$31,0)</f>
-        <v/>
+        <v>0.02109704641350211</v>
       </c>
       <c r="M33" s="64">
         <f>IFERROR(M31/$V$31,0)</f>
-        <v/>
+        <v>0.06282231598687295</v>
       </c>
       <c r="N33" s="64">
         <f>IFERROR(N31/$V$31,0)</f>
-        <v/>
+        <v>0.04688232536333802</v>
       </c>
       <c r="O33" s="64">
         <f>IFERROR(O31/$V$31,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P33" s="64">
         <f>IFERROR(P31/$V$31,0)</f>
-        <v/>
+        <v>0.14814814814814814</v>
       </c>
       <c r="Q33" s="64">
         <f>IFERROR(Q31/$V$31,0)</f>
-        <v/>
+        <v>0.1894045944678856</v>
       </c>
       <c r="R33" s="64">
         <f>IFERROR(R31/$V$31,0)</f>
-        <v/>
+        <v>0.26441631504922647</v>
       </c>
       <c r="S33" s="64">
         <f>IFERROR(S31/$V$31,0)</f>
-        <v/>
+        <v>0.26441631504922647</v>
       </c>
       <c r="T33" s="64">
         <f>IFERROR(T31/$V$31,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U33" s="64">
         <f>IFERROR(U31/$V$31,0)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -20313,9 +20313,9 @@
       <c r="E36" s="65" t="n"/>
       <c r="F36" s="65" t="n"/>
       <c r="G36" s="65" t="n"/>
-      <c r="H36" s="66">
+      <c r="H36" s="66" t="str">
         <f>" All Values in ( "&amp;C7&amp;" )"</f>
-        <v/>
+        <v> All Values in ( INR )</v>
       </c>
       <c r="I36" s="24" t="n"/>
       <c r="L36" s="67" t="inlineStr">
@@ -20411,12 +20411,12 @@
       <c r="P38" s="24" t="n"/>
       <c r="Q38" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>13756660</v>
       </c>
       <c r="R38" s="24" t="n"/>
       <c r="S38" s="55">
         <f>$AB$5</f>
-        <v/>
+        <v>13756660</v>
       </c>
     </row>
     <row r="39">
@@ -20427,24 +20427,24 @@
       </c>
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="24" t="n"/>
-      <c r="D39" s="8">
+      <c r="D39" s="8" t="str">
         <f>C4</f>
-        <v/>
+        <v>India - R&amp;C</v>
       </c>
       <c r="F39" s="31">
         <f>V31</f>
-        <v/>
+        <v>2133</v>
       </c>
       <c r="G39" s="32">
         <f>D37-(SUM(G40:G43)+H44)</f>
-        <v/>
+        <v>4750000</v>
       </c>
       <c r="H39" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="30">
+      <c r="L39" s="30" t="str">
         <f>"Proposed Fee (Home Office)"&amp;" - "&amp;IF(D39=0,"",D39)</f>
-        <v/>
+        <v>Proposed Fee (Home Office) - India - R&amp;C</v>
       </c>
       <c r="M39" s="24" t="n"/>
       <c r="N39" s="24" t="n"/>
@@ -20452,12 +20452,12 @@
       <c r="P39" s="24" t="n"/>
       <c r="Q39" s="12">
         <f>G39</f>
-        <v/>
+        <v>4750000</v>
       </c>
       <c r="R39" s="73" t="n"/>
       <c r="S39" s="11">
         <f>S38*S42</f>
-        <v/>
+        <v>4750000</v>
       </c>
     </row>
     <row r="40">
@@ -20490,12 +20490,12 @@
       <c r="P40" s="24" t="n"/>
       <c r="Q40" s="11">
         <f>Q38-Q39</f>
-        <v/>
+        <v>9006660</v>
       </c>
       <c r="R40" s="24" t="n"/>
       <c r="S40" s="11">
         <f>S38-S39</f>
-        <v/>
+        <v>9006660</v>
       </c>
     </row>
     <row r="41">
@@ -20523,12 +20523,12 @@
       <c r="P41" s="24" t="n"/>
       <c r="Q41" s="74">
         <f>IFERROR(Q40/Q38,0)</f>
-        <v/>
+        <v>0.6547126991580805</v>
       </c>
       <c r="R41" s="24" t="n"/>
       <c r="S41" s="74">
         <f>1-S42</f>
-        <v/>
+        <v>0.6547126991580805</v>
       </c>
     </row>
     <row r="42">
@@ -20556,12 +20556,12 @@
       <c r="P42" s="24" t="n"/>
       <c r="Q42" s="75">
         <f>1-Q41</f>
-        <v/>
+        <v>0.3452873008419195</v>
       </c>
       <c r="R42" s="24" t="n"/>
       <c r="S42" s="76">
         <f>F46</f>
-        <v/>
+        <v>0.3452873008419195</v>
       </c>
     </row>
     <row r="43">
@@ -20596,15 +20596,15 @@
       <c r="E44" s="34" t="n"/>
       <c r="F44" s="78">
         <f>SUM(F39:F43)</f>
-        <v/>
+        <v>2133</v>
       </c>
       <c r="G44" s="79">
         <f>SUM(G39:G43)</f>
-        <v/>
+        <v>4750000</v>
       </c>
       <c r="H44" s="79">
         <f>SUM(H39:H43)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="F46" s="81">
         <f>IFERROR(G39/$AB$5,0)</f>
-        <v/>
+        <v>0.3452873008419195</v>
       </c>
       <c r="G46" s="24" t="n"/>
     </row>
@@ -20690,43 +20690,43 @@
       </c>
     </row>
     <row r="49">
-      <c r="K49" s="67">
+      <c r="K49" s="67" t="str">
         <f>C7</f>
-        <v/>
+        <v>INR</v>
       </c>
       <c r="L49" s="11">
         <f>G44</f>
-        <v/>
+        <v>4750000</v>
       </c>
       <c r="M49" s="10">
         <f>IFERROR(L49/F44,0)</f>
-        <v/>
+        <v>2226.910454758556</v>
       </c>
       <c r="N49" s="11">
         <f>G39</f>
-        <v/>
+        <v>4750000</v>
       </c>
       <c r="O49" s="10">
         <f>IFERROR(N49/V31,0)</f>
-        <v/>
+        <v>2226.910454758556</v>
       </c>
       <c r="P49" s="83">
         <f>IFERROR((T49-(N49*5%))/N49,0)</f>
-        <v/>
+        <v>0.21459452631578949</v>
       </c>
       <c r="Q49" s="84" t="n"/>
       <c r="R49" s="83">
         <f>IFERROR((L49-V49-(G44-G39)-(N49*5%))/L49,0)</f>
-        <v/>
+        <v>0.21459452631578949</v>
       </c>
       <c r="S49" s="84" t="n"/>
       <c r="T49" s="11">
         <f>IFERROR(N49-V49,0)</f>
-        <v/>
+        <v>1256824</v>
       </c>
       <c r="V49" s="11">
         <f>IFERROR($AB$6,0)</f>
-        <v/>
+        <v>3493176</v>
       </c>
     </row>
     <row r="51">
@@ -20841,8 +20841,8 @@
     <mergeCell ref="U6:U7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId2"/>
+    <hyperlink ref="X4" ns1:id="rId1"/>
+    <hyperlink ref="X6" ns1:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
